--- a/작업장소 (영수증 보관)/심천지사 전도금 정산 양식_YYYY-MM.xlsx
+++ b/작업장소 (영수증 보관)/심천지사 전도금 정산 양식_YYYY-MM.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\20000177\Desktop\Wooktigravity\260630_shenzhen_restart_step_1\영수증 보관소\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\20000177\Desktop\Wooktigravity\260630_shenzhen_restart_step_1\작업장소 (영수증 보관)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{366512D2-2657-49A8-A765-F1A488D589C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F9C168-9BC2-4D41-B611-184E8313F698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="603" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="통장내역(환율표)" sheetId="131" r:id="rId1"/>
@@ -6633,6 +6633,27 @@
     <xf numFmtId="179" fontId="76" fillId="2" borderId="27" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="179" fontId="76" fillId="2" borderId="43" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="179" fontId="76" fillId="2" borderId="44" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="137" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="77" fillId="0" borderId="0" xfId="138" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="71" fillId="0" borderId="0" xfId="138" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="187" fontId="12" fillId="15" borderId="27" xfId="138" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="187" fontId="12" fillId="0" borderId="27" xfId="138" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="2" borderId="18" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -6710,27 +6731,6 @@
     </xf>
     <xf numFmtId="0" fontId="67" fillId="2" borderId="14" xfId="176" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="76" fillId="2" borderId="43" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="179" fontId="76" fillId="2" borderId="44" xfId="4" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="71" fillId="0" borderId="0" xfId="137" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="77" fillId="0" borderId="0" xfId="138" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="71" fillId="0" borderId="0" xfId="138" applyNumberFormat="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="187" fontId="12" fillId="15" borderId="27" xfId="138" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="187" fontId="12" fillId="0" borderId="27" xfId="138" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="565">
@@ -7369,950 +7369,6 @@
 </styleSheet>
 </file>
 
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>158750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>603249</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>36703</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="15" name="图片 14">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00000F000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="6953250"/>
-          <a:ext cx="9405937" cy="7736078"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>142876</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>127000</xdr:colOff>
-      <xdr:row>36</xdr:row>
-      <xdr:rowOff>165491</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="14" name="图片 13">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00000E000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="142876" y="0"/>
-          <a:ext cx="8159749" cy="6586929"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>371515</xdr:colOff>
-      <xdr:row>66</xdr:row>
-      <xdr:rowOff>3669</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="7263148" cy="8509715"/>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="그림 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000004000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8601115" y="13833969"/>
-          <a:ext cx="7263148" cy="8509715"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>8657</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>161636</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2493819" cy="346363"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="TextBox 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000005000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15096257" y="20487986"/>
-          <a:ext cx="2493819" cy="346363"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>=&gt; </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>매번 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>10000</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>웬이하 계좌이체시 수수료</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>22</xdr:col>
-      <xdr:colOff>28863</xdr:colOff>
-      <xdr:row>99</xdr:row>
-      <xdr:rowOff>138544</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2493819" cy="346363"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="TextBox 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000006000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15116463" y="20883994"/>
-          <a:ext cx="2493819" cy="346363"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>=&gt; </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>매번 </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>10000</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>웬</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>~100000</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>웬 계좌이체시 수수료</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1594567</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>161326</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2022990" cy="814300"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="TextBox 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000007000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5608674" y="447076"/>
-          <a:ext cx="2022990" cy="814300"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:spAutoFit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="3600" b="1">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>USD </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="3600" b="1">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>내역</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>606626</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>37356</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1387929" cy="389700"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="TextBox 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000008000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1495626" y="2418606"/>
-          <a:ext cx="1387929" cy="389700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>=&gt; </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1600" b="1">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>입금 금액</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1398583</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>47618</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1387929" cy="365191"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="9" name="TextBox 8">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000009000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5422896" y="2952743"/>
-          <a:ext cx="1387929" cy="365191"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1600" b="1">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>=&gt; </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1600" b="1">
-              <a:solidFill>
-                <a:schemeClr val="accent6">
-                  <a:lumMod val="75000"/>
-                </a:schemeClr>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>거래 시간</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2647832</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>172435</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1387929" cy="402760"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="TextBox 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00000A000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6672145" y="8189310"/>
-          <a:ext cx="1387929" cy="402760"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>=&gt; </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>거래</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t> 기간</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>1585018</xdr:colOff>
-      <xdr:row>38</xdr:row>
-      <xdr:rowOff>167140</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="2462893" cy="814945"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="11" name="TextBox 17">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00000B000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="5603661" y="7206569"/>
-          <a:ext cx="2462893" cy="814945"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="square" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="3600" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>RMB </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="3600" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>내역</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:oneCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>2383661</xdr:colOff>
-      <xdr:row>55</xdr:row>
-      <xdr:rowOff>18720</xdr:rowOff>
-    </xdr:from>
-    <xdr:ext cx="1387929" cy="394608"/>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="12" name="TextBox 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00000C000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvSpPr txBox="1"/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6394744" y="10062303"/>
-          <a:ext cx="1387929" cy="394608"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:scrgbClr r="0" g="0" b="0"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:lstStyle/>
-        <a:p>
-          <a:r>
-            <a:rPr lang="en-US" altLang="ko-KR" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>=&gt; </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ko-KR" altLang="en-US" sz="1000" b="1">
-              <a:solidFill>
-                <a:srgbClr val="FF0000"/>
-              </a:solidFill>
-            </a:rPr>
-            <a:t>잔액</a:t>
-          </a:r>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:oneCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>619124</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>119063</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>395384</xdr:colOff>
-      <xdr:row>33</xdr:row>
-      <xdr:rowOff>111125</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="13" name="图片 12">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-00000D000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId4"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="8167687" y="119063"/>
-          <a:ext cx="7324822" cy="5889625"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>83</xdr:row>
-      <xdr:rowOff>31750</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>476250</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>105569</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="16" name="图片 15">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000010000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="14684375"/>
-          <a:ext cx="9278938" cy="2518569"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>97</xdr:row>
-      <xdr:rowOff>87313</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>484186</xdr:colOff>
-      <xdr:row>112</xdr:row>
-      <xdr:rowOff>2441</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="17" name="图片 16">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000011000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId6"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="17184688"/>
-          <a:ext cx="9286874" cy="2534503"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>111</xdr:row>
-      <xdr:rowOff>75406</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>508000</xdr:colOff>
-      <xdr:row>120</xdr:row>
-      <xdr:rowOff>69712</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="22" name="图片 21">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{00000000-0008-0000-0700-000016000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId7"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="23911719"/>
-          <a:ext cx="10175875" cy="1923118"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
 <file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
 <externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" mc:Ignorable="x14">
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
@@ -8845,34 +7901,34 @@
   <sheetData>
     <row r="1" spans="2:14" ht="6.6" customHeight="1" thickBot="1"/>
     <row r="2" spans="2:14" ht="16.5" customHeight="1">
-      <c r="B2" s="621" t="s">
+      <c r="B2" s="628" t="s">
         <v>300</v>
       </c>
-      <c r="C2" s="623" t="s">
+      <c r="C2" s="630" t="s">
         <v>301</v>
       </c>
-      <c r="D2" s="624"/>
-      <c r="E2" s="620"/>
-      <c r="F2" s="623" t="s">
+      <c r="D2" s="631"/>
+      <c r="E2" s="627"/>
+      <c r="F2" s="630" t="s">
         <v>302</v>
       </c>
-      <c r="G2" s="624"/>
-      <c r="H2" s="620"/>
-      <c r="I2" s="623" t="s">
+      <c r="G2" s="631"/>
+      <c r="H2" s="627"/>
+      <c r="I2" s="630" t="s">
         <v>303</v>
       </c>
-      <c r="J2" s="620"/>
-      <c r="K2" s="623" t="s">
+      <c r="J2" s="627"/>
+      <c r="K2" s="630" t="s">
         <v>304</v>
       </c>
-      <c r="L2" s="620"/>
-      <c r="M2" s="619" t="s">
+      <c r="L2" s="627"/>
+      <c r="M2" s="626" t="s">
         <v>305</v>
       </c>
-      <c r="N2" s="620"/>
+      <c r="N2" s="627"/>
     </row>
     <row r="3" spans="2:14" ht="27" customHeight="1">
-      <c r="B3" s="622"/>
+      <c r="B3" s="629"/>
       <c r="C3" s="541" t="s">
         <v>306</v>
       </c>
@@ -11241,309 +10297,231 @@
       <c r="E5" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="F5" s="409">
-        <v>6</v>
-      </c>
+      <c r="F5" s="409"/>
       <c r="G5" s="409">
         <f>F5*20</f>
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="H5" s="409"/>
-      <c r="J5" s="410">
-        <v>46135</v>
-      </c>
+      <c r="J5" s="410"/>
       <c r="K5" s="409"/>
       <c r="L5" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="M5" s="409">
-        <v>4</v>
-      </c>
+      <c r="M5" s="409"/>
       <c r="N5" s="409">
         <f t="shared" ref="N5:N16" si="0">M5*20</f>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O5" s="409"/>
-      <c r="Q5" s="410">
-        <v>46134</v>
-      </c>
+      <c r="Q5" s="410"/>
       <c r="R5" s="409"/>
       <c r="S5" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="T5" s="409">
-        <v>1</v>
-      </c>
+      <c r="T5" s="409"/>
       <c r="U5" s="409">
         <f t="shared" ref="U5:U16" si="1">T5*20</f>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V5" s="409"/>
     </row>
     <row r="6" spans="3:22">
-      <c r="C6" s="410">
-        <v>46135</v>
-      </c>
+      <c r="C6" s="410"/>
       <c r="D6" s="409"/>
       <c r="E6" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="F6" s="409">
-        <v>3.5</v>
-      </c>
+      <c r="F6" s="409"/>
       <c r="G6" s="409">
         <f>F6*20</f>
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="H6" s="409"/>
-      <c r="J6" s="410">
-        <v>46139</v>
-      </c>
+      <c r="J6" s="410"/>
       <c r="K6" s="409"/>
       <c r="L6" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="M6" s="409">
-        <v>4</v>
-      </c>
+      <c r="M6" s="409"/>
       <c r="N6" s="409">
         <f t="shared" si="0"/>
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="O6" s="409"/>
-      <c r="Q6" s="410">
-        <v>46135</v>
-      </c>
+      <c r="Q6" s="410"/>
       <c r="R6" s="409"/>
       <c r="S6" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="T6" s="409">
-        <v>2</v>
-      </c>
+      <c r="T6" s="409"/>
       <c r="U6" s="409">
         <f t="shared" si="1"/>
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="V6" s="409"/>
     </row>
     <row r="7" spans="3:22">
-      <c r="C7" s="410">
-        <v>46136</v>
-      </c>
+      <c r="C7" s="410"/>
       <c r="D7" s="409"/>
       <c r="E7" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="F7" s="409">
-        <v>6.5</v>
-      </c>
+      <c r="F7" s="409"/>
       <c r="G7" s="409">
         <f t="shared" ref="G7:G14" si="2">F7*20</f>
-        <v>130</v>
+        <v>0</v>
       </c>
       <c r="H7" s="409"/>
-      <c r="J7" s="410">
-        <v>46149</v>
-      </c>
+      <c r="J7" s="410"/>
       <c r="K7" s="409"/>
       <c r="L7" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="M7" s="409">
-        <v>3</v>
-      </c>
+      <c r="M7" s="409"/>
       <c r="N7" s="409">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O7" s="409"/>
-      <c r="Q7" s="410">
-        <v>46139</v>
-      </c>
+      <c r="Q7" s="410"/>
       <c r="R7" s="409"/>
       <c r="S7" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="T7" s="409">
-        <v>3</v>
-      </c>
+      <c r="T7" s="409"/>
       <c r="U7" s="409">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V7" s="409"/>
     </row>
     <row r="8" spans="3:22">
-      <c r="C8" s="410">
-        <v>46139</v>
-      </c>
+      <c r="C8" s="410"/>
       <c r="D8" s="409"/>
       <c r="E8" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="F8" s="409">
-        <v>3</v>
-      </c>
+      <c r="F8" s="409"/>
       <c r="G8" s="409">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H8" s="409"/>
-      <c r="J8" s="410">
-        <v>46150</v>
-      </c>
+      <c r="J8" s="410"/>
       <c r="K8" s="409"/>
       <c r="L8" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="M8" s="409">
-        <v>3</v>
-      </c>
+      <c r="M8" s="409"/>
       <c r="N8" s="409">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O8" s="409"/>
-      <c r="Q8" s="410">
-        <v>46140</v>
-      </c>
+      <c r="Q8" s="410"/>
       <c r="R8" s="409"/>
       <c r="S8" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="T8" s="409">
-        <v>1</v>
-      </c>
+      <c r="T8" s="409"/>
       <c r="U8" s="409">
         <f t="shared" si="1"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="V8" s="409"/>
     </row>
     <row r="9" spans="3:22">
-      <c r="C9" s="410">
-        <v>46142</v>
-      </c>
+      <c r="C9" s="410"/>
       <c r="D9" s="409"/>
       <c r="E9" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="F9" s="409">
-        <v>1</v>
-      </c>
+      <c r="F9" s="409"/>
       <c r="G9" s="409">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H9" s="411"/>
-      <c r="J9" s="410">
-        <v>46155</v>
-      </c>
+      <c r="J9" s="410"/>
       <c r="K9" s="409"/>
       <c r="L9" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="M9" s="409">
-        <v>5</v>
-      </c>
+      <c r="M9" s="409"/>
       <c r="N9" s="409">
         <f t="shared" si="0"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="O9" s="411"/>
-      <c r="Q9" s="410">
-        <v>46154</v>
-      </c>
+      <c r="Q9" s="410"/>
       <c r="R9" s="409"/>
       <c r="S9" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="T9" s="409">
-        <v>3</v>
-      </c>
+      <c r="T9" s="409"/>
       <c r="U9" s="409">
         <f t="shared" si="1"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="V9" s="411"/>
     </row>
     <row r="10" spans="3:22">
-      <c r="C10" s="410">
-        <v>46150</v>
-      </c>
+      <c r="C10" s="410"/>
       <c r="D10" s="409"/>
       <c r="E10" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="F10" s="409">
-        <v>5</v>
-      </c>
+      <c r="F10" s="409"/>
       <c r="G10" s="409">
         <f t="shared" si="2"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="H10" s="409"/>
-      <c r="J10" s="410">
-        <v>46158</v>
-      </c>
+      <c r="J10" s="410"/>
       <c r="K10" s="409"/>
       <c r="L10" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="M10" s="409">
-        <v>16</v>
-      </c>
+      <c r="M10" s="409"/>
       <c r="N10" s="409">
         <f t="shared" si="0"/>
-        <v>320</v>
+        <v>0</v>
       </c>
       <c r="O10" s="409"/>
-      <c r="Q10" s="410">
-        <v>46158</v>
-      </c>
+      <c r="Q10" s="410"/>
       <c r="R10" s="409"/>
       <c r="S10" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="T10" s="409">
-        <v>5</v>
-      </c>
+      <c r="T10" s="409"/>
       <c r="U10" s="409">
         <f t="shared" si="1"/>
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="V10" s="409"/>
     </row>
     <row r="11" spans="3:22">
-      <c r="C11" s="410">
-        <v>46153</v>
-      </c>
+      <c r="C11" s="410"/>
       <c r="D11" s="409"/>
       <c r="E11" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="F11" s="409">
-        <v>1</v>
-      </c>
+      <c r="F11" s="409"/>
       <c r="G11" s="409">
         <f t="shared" si="2"/>
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="H11" s="409"/>
-      <c r="J11" s="410">
-        <v>46159</v>
-      </c>
+      <c r="J11" s="410"/>
       <c r="K11" s="409"/>
       <c r="L11" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="M11" s="409">
-        <v>3</v>
-      </c>
+      <c r="M11" s="409"/>
       <c r="N11" s="409">
         <f t="shared" si="0"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="O11" s="409"/>
       <c r="Q11" s="410"/>
@@ -11559,19 +10537,15 @@
       <c r="V11" s="409"/>
     </row>
     <row r="12" spans="3:22">
-      <c r="C12" s="410">
-        <v>46156</v>
-      </c>
+      <c r="C12" s="410"/>
       <c r="D12" s="409"/>
       <c r="E12" s="409" t="s">
         <v>60</v>
       </c>
-      <c r="F12" s="409">
-        <v>3</v>
-      </c>
+      <c r="F12" s="409"/>
       <c r="G12" s="409">
         <f t="shared" si="2"/>
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="H12" s="409"/>
       <c r="J12" s="410"/>
@@ -11985,15 +10959,15 @@
     <row r="24" spans="3:22">
       <c r="G24" s="413">
         <f>SUM(G5:G23)</f>
-        <v>580</v>
+        <v>0</v>
       </c>
       <c r="N24" s="413">
         <f>SUM(N5:N23)</f>
-        <v>760</v>
+        <v>0</v>
       </c>
       <c r="U24" s="413">
         <f>SUM(U5:U23)</f>
-        <v>300</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -12876,22 +11850,22 @@
       <c r="G17" s="70" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="625" t="s">
+      <c r="H17" s="632" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="626"/>
-      <c r="J17" s="626"/>
-      <c r="K17" s="625" t="s">
+      <c r="I17" s="633"/>
+      <c r="J17" s="633"/>
+      <c r="K17" s="632" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="626"/>
-      <c r="M17" s="627"/>
-      <c r="N17" s="628" t="s">
+      <c r="L17" s="633"/>
+      <c r="M17" s="634"/>
+      <c r="N17" s="635" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="629"/>
-      <c r="P17" s="630"/>
-      <c r="Q17" s="630"/>
+      <c r="O17" s="636"/>
+      <c r="P17" s="637"/>
+      <c r="Q17" s="637"/>
       <c r="R17" s="71" t="s">
         <v>103</v>
       </c>
@@ -12940,10 +11914,10 @@
       <c r="O18" s="88" t="s">
         <v>19</v>
       </c>
-      <c r="P18" s="631" t="s">
+      <c r="P18" s="638" t="s">
         <v>18</v>
       </c>
-      <c r="Q18" s="631"/>
+      <c r="Q18" s="638"/>
       <c r="R18" s="134" t="s">
         <v>103</v>
       </c>
@@ -18339,22 +17313,22 @@
       <c r="G17" s="242" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="632" t="s">
+      <c r="H17" s="639" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="632"/>
-      <c r="J17" s="632"/>
-      <c r="K17" s="632" t="s">
+      <c r="I17" s="639"/>
+      <c r="J17" s="639"/>
+      <c r="K17" s="639" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="632"/>
-      <c r="M17" s="633"/>
-      <c r="N17" s="634" t="s">
+      <c r="L17" s="639"/>
+      <c r="M17" s="640"/>
+      <c r="N17" s="641" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="634"/>
-      <c r="P17" s="635"/>
-      <c r="Q17" s="635"/>
+      <c r="O17" s="641"/>
+      <c r="P17" s="642"/>
+      <c r="Q17" s="642"/>
       <c r="R17" s="242" t="s">
         <v>103</v>
       </c>
@@ -18403,10 +17377,10 @@
       <c r="O18" s="249" t="s">
         <v>19</v>
       </c>
-      <c r="P18" s="636" t="s">
+      <c r="P18" s="643" t="s">
         <v>18</v>
       </c>
-      <c r="Q18" s="636"/>
+      <c r="Q18" s="643"/>
       <c r="R18" s="246" t="s">
         <v>103</v>
       </c>
@@ -23330,22 +22304,22 @@
       <c r="G17" s="242" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="632" t="s">
+      <c r="H17" s="639" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="632"/>
-      <c r="J17" s="632"/>
-      <c r="K17" s="632" t="s">
+      <c r="I17" s="639"/>
+      <c r="J17" s="639"/>
+      <c r="K17" s="639" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="632"/>
-      <c r="M17" s="633"/>
-      <c r="N17" s="634" t="s">
+      <c r="L17" s="639"/>
+      <c r="M17" s="640"/>
+      <c r="N17" s="641" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="634"/>
-      <c r="P17" s="635"/>
-      <c r="Q17" s="635"/>
+      <c r="O17" s="641"/>
+      <c r="P17" s="642"/>
+      <c r="Q17" s="642"/>
       <c r="R17" s="242" t="s">
         <v>103</v>
       </c>
@@ -23394,10 +22368,10 @@
       <c r="O18" s="249" t="s">
         <v>19</v>
       </c>
-      <c r="P18" s="636" t="s">
+      <c r="P18" s="643" t="s">
         <v>18</v>
       </c>
-      <c r="Q18" s="636"/>
+      <c r="Q18" s="643"/>
       <c r="R18" s="246" t="s">
         <v>103</v>
       </c>
@@ -28863,22 +27837,22 @@
       <c r="G17" s="242" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="632" t="s">
+      <c r="H17" s="639" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="632"/>
-      <c r="J17" s="632"/>
-      <c r="K17" s="632" t="s">
+      <c r="I17" s="639"/>
+      <c r="J17" s="639"/>
+      <c r="K17" s="639" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="632"/>
-      <c r="M17" s="633"/>
-      <c r="N17" s="634" t="s">
+      <c r="L17" s="639"/>
+      <c r="M17" s="640"/>
+      <c r="N17" s="641" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="634"/>
-      <c r="P17" s="635"/>
-      <c r="Q17" s="635"/>
+      <c r="O17" s="641"/>
+      <c r="P17" s="642"/>
+      <c r="Q17" s="642"/>
       <c r="R17" s="242" t="s">
         <v>103</v>
       </c>
@@ -28927,10 +27901,10 @@
       <c r="O18" s="249" t="s">
         <v>19</v>
       </c>
-      <c r="P18" s="636" t="s">
+      <c r="P18" s="643" t="s">
         <v>18</v>
       </c>
-      <c r="Q18" s="636"/>
+      <c r="Q18" s="643"/>
       <c r="R18" s="246" t="s">
         <v>103</v>
       </c>
@@ -34507,22 +33481,22 @@
       <c r="G17" s="242" t="s">
         <v>1</v>
       </c>
-      <c r="H17" s="632" t="s">
+      <c r="H17" s="639" t="s">
         <v>15</v>
       </c>
-      <c r="I17" s="632"/>
-      <c r="J17" s="632"/>
-      <c r="K17" s="632" t="s">
+      <c r="I17" s="639"/>
+      <c r="J17" s="639"/>
+      <c r="K17" s="639" t="s">
         <v>16</v>
       </c>
-      <c r="L17" s="632"/>
-      <c r="M17" s="633"/>
-      <c r="N17" s="634" t="s">
+      <c r="L17" s="639"/>
+      <c r="M17" s="640"/>
+      <c r="N17" s="641" t="s">
         <v>17</v>
       </c>
-      <c r="O17" s="634"/>
-      <c r="P17" s="635"/>
-      <c r="Q17" s="635"/>
+      <c r="O17" s="641"/>
+      <c r="P17" s="642"/>
+      <c r="Q17" s="642"/>
       <c r="R17" s="242" t="s">
         <v>103</v>
       </c>
@@ -34571,10 +33545,10 @@
       <c r="O18" s="249" t="s">
         <v>19</v>
       </c>
-      <c r="P18" s="636" t="s">
+      <c r="P18" s="643" t="s">
         <v>18</v>
       </c>
-      <c r="Q18" s="636"/>
+      <c r="Q18" s="643"/>
       <c r="R18" s="246" t="s">
         <v>103</v>
       </c>
@@ -38178,7 +37152,7 @@
         <v>131</v>
       </c>
       <c r="Q79" s="388"/>
-      <c r="R79" s="637" t="s">
+      <c r="R79" s="644" t="s">
         <v>213</v>
       </c>
       <c r="S79" s="129" t="e">
@@ -38238,7 +37212,7 @@
         <v>131</v>
       </c>
       <c r="Q80" s="388"/>
-      <c r="R80" s="638"/>
+      <c r="R80" s="645"/>
       <c r="S80" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38296,7 +37270,7 @@
         <v>131</v>
       </c>
       <c r="Q81" s="388"/>
-      <c r="R81" s="638"/>
+      <c r="R81" s="645"/>
       <c r="S81" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38354,7 +37328,7 @@
         <v>131</v>
       </c>
       <c r="Q82" s="388"/>
-      <c r="R82" s="638"/>
+      <c r="R82" s="645"/>
       <c r="S82" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38412,7 +37386,7 @@
         <v>131</v>
       </c>
       <c r="Q83" s="388"/>
-      <c r="R83" s="638"/>
+      <c r="R83" s="645"/>
       <c r="S83" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38470,7 +37444,7 @@
         <v>131</v>
       </c>
       <c r="Q84" s="388"/>
-      <c r="R84" s="637" t="s">
+      <c r="R84" s="644" t="s">
         <v>115</v>
       </c>
       <c r="S84" s="129" t="e">
@@ -38530,7 +37504,7 @@
         <v>131</v>
       </c>
       <c r="Q85" s="388"/>
-      <c r="R85" s="638"/>
+      <c r="R85" s="645"/>
       <c r="S85" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38588,7 +37562,7 @@
         <v>131</v>
       </c>
       <c r="Q86" s="388"/>
-      <c r="R86" s="638"/>
+      <c r="R86" s="645"/>
       <c r="S86" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38646,7 +37620,7 @@
         <v>131</v>
       </c>
       <c r="Q87" s="388"/>
-      <c r="R87" s="638"/>
+      <c r="R87" s="645"/>
       <c r="S87" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38704,7 +37678,7 @@
         <v>131</v>
       </c>
       <c r="Q88" s="388"/>
-      <c r="R88" s="638"/>
+      <c r="R88" s="645"/>
       <c r="S88" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38762,7 +37736,7 @@
         <v>131</v>
       </c>
       <c r="Q89" s="388"/>
-      <c r="R89" s="637" t="s">
+      <c r="R89" s="644" t="s">
         <v>195</v>
       </c>
       <c r="S89" s="129" t="e">
@@ -38821,7 +37795,7 @@
         <v>131</v>
       </c>
       <c r="Q90" s="388"/>
-      <c r="R90" s="637"/>
+      <c r="R90" s="644"/>
       <c r="S90" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38868,7 +37842,7 @@
         <v>131</v>
       </c>
       <c r="Q91" s="388"/>
-      <c r="R91" s="638"/>
+      <c r="R91" s="645"/>
       <c r="S91" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38915,7 +37889,7 @@
         <v>131</v>
       </c>
       <c r="Q92" s="388"/>
-      <c r="R92" s="638"/>
+      <c r="R92" s="645"/>
       <c r="S92" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -38962,7 +37936,7 @@
         <v>131</v>
       </c>
       <c r="Q93" s="388"/>
-      <c r="R93" s="638"/>
+      <c r="R93" s="645"/>
       <c r="S93" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39009,7 +37983,7 @@
         <v>131</v>
       </c>
       <c r="Q94" s="388"/>
-      <c r="R94" s="639" t="s">
+      <c r="R94" s="646" t="s">
         <v>196</v>
       </c>
       <c r="S94" s="129" t="e">
@@ -39058,7 +38032,7 @@
         <v>131</v>
       </c>
       <c r="Q95" s="388"/>
-      <c r="R95" s="637"/>
+      <c r="R95" s="644"/>
       <c r="S95" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39105,7 +38079,7 @@
         <v>131</v>
       </c>
       <c r="Q96" s="388"/>
-      <c r="R96" s="638"/>
+      <c r="R96" s="645"/>
       <c r="S96" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39152,7 +38126,7 @@
         <v>131</v>
       </c>
       <c r="Q97" s="388"/>
-      <c r="R97" s="638"/>
+      <c r="R97" s="645"/>
       <c r="S97" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39199,7 +38173,7 @@
         <v>131</v>
       </c>
       <c r="Q98" s="388"/>
-      <c r="R98" s="638"/>
+      <c r="R98" s="645"/>
       <c r="S98" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39246,7 +38220,7 @@
         <v>131</v>
       </c>
       <c r="Q99" s="388"/>
-      <c r="R99" s="637" t="s">
+      <c r="R99" s="644" t="s">
         <v>197</v>
       </c>
       <c r="S99" s="129" t="e">
@@ -39295,7 +38269,7 @@
         <v>131</v>
       </c>
       <c r="Q100" s="388"/>
-      <c r="R100" s="637"/>
+      <c r="R100" s="644"/>
       <c r="S100" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39342,7 +38316,7 @@
         <v>131</v>
       </c>
       <c r="Q101" s="388"/>
-      <c r="R101" s="638"/>
+      <c r="R101" s="645"/>
       <c r="S101" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39389,7 +38363,7 @@
         <v>131</v>
       </c>
       <c r="Q102" s="388"/>
-      <c r="R102" s="638"/>
+      <c r="R102" s="645"/>
       <c r="S102" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39436,7 +38410,7 @@
         <v>131</v>
       </c>
       <c r="Q103" s="388"/>
-      <c r="R103" s="637" t="s">
+      <c r="R103" s="644" t="s">
         <v>198</v>
       </c>
       <c r="S103" s="129" t="e">
@@ -39485,7 +38459,7 @@
         <v>131</v>
       </c>
       <c r="Q104" s="388"/>
-      <c r="R104" s="637"/>
+      <c r="R104" s="644"/>
       <c r="S104" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39532,7 +38506,7 @@
         <v>131</v>
       </c>
       <c r="Q105" s="388"/>
-      <c r="R105" s="638"/>
+      <c r="R105" s="645"/>
       <c r="S105" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39590,7 +38564,7 @@
         <v>131</v>
       </c>
       <c r="Q106" s="388"/>
-      <c r="R106" s="638"/>
+      <c r="R106" s="645"/>
       <c r="S106" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39648,7 +38622,7 @@
         <v>131</v>
       </c>
       <c r="Q107" s="388"/>
-      <c r="R107" s="638"/>
+      <c r="R107" s="645"/>
       <c r="S107" s="129" t="e">
         <f t="shared" si="12"/>
         <v>#REF!</v>
@@ -39856,17 +38830,17 @@
     </sortState>
   </autoFilter>
   <mergeCells count="11">
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
     <mergeCell ref="R103:R107"/>
     <mergeCell ref="R79:R83"/>
     <mergeCell ref="R84:R88"/>
     <mergeCell ref="R89:R93"/>
     <mergeCell ref="R94:R98"/>
     <mergeCell ref="R99:R102"/>
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -39924,7 +38898,7 @@
       <c r="P1" s="437"/>
       <c r="Q1" s="437"/>
       <c r="R1" s="438"/>
-      <c r="S1" s="649"/>
+      <c r="S1" s="621"/>
     </row>
     <row r="2" spans="1:22" ht="15" customHeight="1">
       <c r="B2" s="441" t="s">
@@ -39969,7 +38943,7 @@
       </c>
       <c r="Q3" s="453"/>
       <c r="R3" s="453"/>
-      <c r="S3" s="650"/>
+      <c r="S3" s="622"/>
     </row>
     <row r="4" spans="1:22" ht="11.25" customHeight="1">
       <c r="A4" s="427"/>
@@ -40045,7 +39019,7 @@
       <c r="P5" s="457"/>
       <c r="Q5" s="453"/>
       <c r="R5" s="453"/>
-      <c r="S5" s="651">
+      <c r="S5" s="623">
         <f>F5+L5+R5</f>
         <v>0</v>
       </c>
@@ -40085,7 +39059,7 @@
       <c r="P6" s="457"/>
       <c r="Q6" s="453"/>
       <c r="R6" s="453"/>
-      <c r="S6" s="651">
+      <c r="S6" s="623">
         <f>F6+L6+R6</f>
         <v>0</v>
       </c>
@@ -40127,7 +39101,7 @@
       <c r="P7" s="457"/>
       <c r="Q7" s="453"/>
       <c r="R7" s="453"/>
-      <c r="S7" s="651">
+      <c r="S7" s="623">
         <f>F7+L7+R7</f>
         <v>0</v>
       </c>
@@ -40167,7 +39141,7 @@
       <c r="P8" s="457"/>
       <c r="Q8" s="453"/>
       <c r="R8" s="453"/>
-      <c r="S8" s="651">
+      <c r="S8" s="623">
         <f>F8+L8+R8</f>
         <v>0</v>
       </c>
@@ -40207,7 +39181,7 @@
       <c r="P9" s="457"/>
       <c r="Q9" s="453"/>
       <c r="R9" s="453"/>
-      <c r="S9" s="651"/>
+      <c r="S9" s="623"/>
     </row>
     <row r="10" spans="1:22" ht="11.25" customHeight="1">
       <c r="A10" s="451">
@@ -40240,7 +39214,7 @@
       <c r="P10" s="457"/>
       <c r="Q10" s="453"/>
       <c r="R10" s="453"/>
-      <c r="S10" s="651"/>
+      <c r="S10" s="623"/>
       <c r="U10" s="446"/>
       <c r="V10" s="444"/>
     </row>
@@ -40307,7 +39281,7 @@
       <c r="P12" s="457"/>
       <c r="Q12" s="487"/>
       <c r="R12" s="453"/>
-      <c r="S12" s="651"/>
+      <c r="S12" s="623"/>
       <c r="U12" s="446"/>
       <c r="V12" s="444"/>
     </row>
@@ -40349,7 +39323,7 @@
       <c r="P13" s="457"/>
       <c r="Q13" s="487"/>
       <c r="R13" s="453"/>
-      <c r="S13" s="651"/>
+      <c r="S13" s="623"/>
       <c r="U13" s="446"/>
       <c r="V13" s="444"/>
     </row>
@@ -40396,7 +39370,7 @@
       <c r="O14" s="457"/>
       <c r="P14" s="457"/>
       <c r="R14" s="457"/>
-      <c r="S14" s="651"/>
+      <c r="S14" s="623"/>
       <c r="U14" s="502"/>
     </row>
     <row r="15" spans="1:22" ht="13.5">
@@ -40512,24 +39486,24 @@
       <c r="I19" s="514" t="s">
         <v>1</v>
       </c>
-      <c r="J19" s="640" t="s">
+      <c r="J19" s="647" t="s">
         <v>15</v>
       </c>
-      <c r="K19" s="640"/>
-      <c r="L19" s="640"/>
-      <c r="M19" s="640" t="s">
+      <c r="K19" s="647"/>
+      <c r="L19" s="647"/>
+      <c r="M19" s="647" t="s">
         <v>16</v>
       </c>
-      <c r="N19" s="640"/>
-      <c r="O19" s="641"/>
-      <c r="P19" s="642" t="s">
+      <c r="N19" s="647"/>
+      <c r="O19" s="648"/>
+      <c r="P19" s="649" t="s">
         <v>17</v>
       </c>
-      <c r="Q19" s="642"/>
-      <c r="R19" s="647" t="s">
+      <c r="Q19" s="649"/>
+      <c r="R19" s="619" t="s">
         <v>18</v>
       </c>
-      <c r="S19" s="648" t="s">
+      <c r="S19" s="620" t="s">
         <v>316</v>
       </c>
       <c r="T19" s="451"/>
@@ -40613,7 +39587,7 @@
         <v>0</v>
       </c>
       <c r="R21" s="617"/>
-      <c r="S21" s="652"/>
+      <c r="S21" s="624"/>
       <c r="T21" s="518"/>
       <c r="U21" s="439"/>
       <c r="V21" s="439"/>
@@ -40642,7 +39616,7 @@
       </c>
       <c r="Q22" s="605"/>
       <c r="R22" s="606"/>
-      <c r="S22" s="653"/>
+      <c r="S22" s="625"/>
       <c r="T22" s="518"/>
       <c r="U22" s="439"/>
       <c r="V22" s="439"/>
@@ -40671,7 +39645,7 @@
       </c>
       <c r="Q23" s="605"/>
       <c r="R23" s="606"/>
-      <c r="S23" s="653"/>
+      <c r="S23" s="625"/>
       <c r="T23" s="518"/>
       <c r="U23" s="538"/>
       <c r="V23" s="538"/>
@@ -40700,7 +39674,7 @@
       </c>
       <c r="Q24" s="605"/>
       <c r="R24" s="606"/>
-      <c r="S24" s="653"/>
+      <c r="S24" s="625"/>
       <c r="T24" s="518"/>
       <c r="U24" s="538"/>
       <c r="V24" s="538"/>
@@ -40729,7 +39703,7 @@
       </c>
       <c r="Q25" s="605"/>
       <c r="R25" s="606"/>
-      <c r="S25" s="653"/>
+      <c r="S25" s="625"/>
       <c r="T25" s="518"/>
       <c r="U25" s="538"/>
       <c r="V25" s="538"/>
@@ -40758,7 +39732,7 @@
       </c>
       <c r="Q26" s="605"/>
       <c r="R26" s="606"/>
-      <c r="S26" s="653"/>
+      <c r="S26" s="625"/>
       <c r="T26" s="518"/>
       <c r="U26" s="538"/>
       <c r="V26" s="538"/>
@@ -40787,7 +39761,7 @@
       </c>
       <c r="Q27" s="605"/>
       <c r="R27" s="606"/>
-      <c r="S27" s="653"/>
+      <c r="S27" s="625"/>
       <c r="T27" s="518"/>
       <c r="U27" s="538"/>
       <c r="V27" s="538"/>
@@ -40816,7 +39790,7 @@
       </c>
       <c r="Q28" s="605"/>
       <c r="R28" s="606"/>
-      <c r="S28" s="653"/>
+      <c r="S28" s="625"/>
       <c r="T28" s="518"/>
       <c r="U28" s="538"/>
       <c r="V28" s="538"/>
@@ -40845,7 +39819,7 @@
       </c>
       <c r="Q29" s="605"/>
       <c r="R29" s="606"/>
-      <c r="S29" s="653"/>
+      <c r="S29" s="625"/>
       <c r="T29" s="518"/>
       <c r="U29" s="538"/>
       <c r="V29" s="538"/>
@@ -40874,7 +39848,7 @@
       </c>
       <c r="Q30" s="605"/>
       <c r="R30" s="606"/>
-      <c r="S30" s="653"/>
+      <c r="S30" s="625"/>
       <c r="T30" s="518"/>
       <c r="U30" s="538"/>
       <c r="V30" s="538"/>
@@ -40905,7 +39879,7 @@
       </c>
       <c r="Q31" s="605"/>
       <c r="R31" s="606"/>
-      <c r="S31" s="653"/>
+      <c r="S31" s="625"/>
       <c r="T31" s="518"/>
       <c r="U31" s="538"/>
       <c r="V31" s="538"/>
@@ -40934,7 +39908,7 @@
       </c>
       <c r="Q32" s="605"/>
       <c r="R32" s="606"/>
-      <c r="S32" s="653"/>
+      <c r="S32" s="625"/>
       <c r="T32" s="518"/>
       <c r="U32" s="538"/>
       <c r="V32" s="538"/>
@@ -40963,7 +39937,7 @@
       </c>
       <c r="Q33" s="605"/>
       <c r="R33" s="606"/>
-      <c r="S33" s="653"/>
+      <c r="S33" s="625"/>
       <c r="T33" s="518"/>
       <c r="U33" s="538"/>
       <c r="V33" s="538"/>
@@ -40992,7 +39966,7 @@
       </c>
       <c r="Q34" s="605"/>
       <c r="R34" s="606"/>
-      <c r="S34" s="653"/>
+      <c r="S34" s="625"/>
       <c r="T34" s="518"/>
       <c r="U34" s="538"/>
       <c r="V34" s="538"/>
@@ -41021,7 +39995,7 @@
       </c>
       <c r="Q35" s="605"/>
       <c r="R35" s="606"/>
-      <c r="S35" s="653"/>
+      <c r="S35" s="625"/>
       <c r="T35" s="518"/>
       <c r="U35" s="538"/>
       <c r="V35" s="538"/>
@@ -41050,7 +40024,7 @@
       </c>
       <c r="Q36" s="605"/>
       <c r="R36" s="606"/>
-      <c r="S36" s="653"/>
+      <c r="S36" s="625"/>
       <c r="T36" s="518"/>
       <c r="U36" s="538"/>
       <c r="V36" s="538"/>
@@ -41079,7 +40053,7 @@
       </c>
       <c r="Q37" s="605"/>
       <c r="R37" s="606"/>
-      <c r="S37" s="653"/>
+      <c r="S37" s="625"/>
       <c r="T37" s="518"/>
       <c r="U37" s="538"/>
       <c r="V37" s="538"/>
@@ -41108,7 +40082,7 @@
       </c>
       <c r="Q38" s="605"/>
       <c r="R38" s="606"/>
-      <c r="S38" s="653"/>
+      <c r="S38" s="625"/>
       <c r="T38" s="518"/>
       <c r="U38" s="538"/>
       <c r="V38" s="538"/>
@@ -41137,7 +40111,7 @@
       </c>
       <c r="Q39" s="605"/>
       <c r="R39" s="606"/>
-      <c r="S39" s="653"/>
+      <c r="S39" s="625"/>
       <c r="T39" s="518"/>
       <c r="U39" s="439"/>
       <c r="V39" s="439"/>
@@ -41166,7 +40140,7 @@
       </c>
       <c r="Q40" s="605"/>
       <c r="R40" s="606"/>
-      <c r="S40" s="653"/>
+      <c r="S40" s="625"/>
       <c r="T40" s="518"/>
       <c r="U40" s="538"/>
       <c r="V40" s="538"/>
@@ -41195,7 +40169,7 @@
       </c>
       <c r="Q41" s="605"/>
       <c r="R41" s="606"/>
-      <c r="S41" s="653"/>
+      <c r="S41" s="625"/>
       <c r="T41" s="518"/>
       <c r="U41" s="538"/>
       <c r="V41" s="538"/>
@@ -41224,7 +40198,7 @@
       </c>
       <c r="Q42" s="605"/>
       <c r="R42" s="606"/>
-      <c r="S42" s="653"/>
+      <c r="S42" s="625"/>
       <c r="T42" s="518"/>
       <c r="U42" s="538"/>
       <c r="V42" s="538"/>
@@ -41253,7 +40227,7 @@
       </c>
       <c r="Q43" s="605"/>
       <c r="R43" s="606"/>
-      <c r="S43" s="653"/>
+      <c r="S43" s="625"/>
       <c r="T43" s="518"/>
       <c r="U43" s="538"/>
       <c r="V43" s="538"/>
@@ -41282,7 +40256,7 @@
       </c>
       <c r="Q44" s="605"/>
       <c r="R44" s="606"/>
-      <c r="S44" s="653"/>
+      <c r="S44" s="625"/>
       <c r="T44" s="518"/>
       <c r="U44" s="538"/>
       <c r="V44" s="538"/>
@@ -41311,7 +40285,7 @@
       </c>
       <c r="Q45" s="605"/>
       <c r="R45" s="606"/>
-      <c r="S45" s="653"/>
+      <c r="S45" s="625"/>
       <c r="T45" s="518"/>
       <c r="U45" s="538"/>
       <c r="V45" s="538"/>
@@ -41340,7 +40314,7 @@
       </c>
       <c r="Q46" s="605"/>
       <c r="R46" s="606"/>
-      <c r="S46" s="653"/>
+      <c r="S46" s="625"/>
       <c r="T46" s="518"/>
       <c r="U46" s="538"/>
       <c r="V46" s="538"/>
@@ -41369,7 +40343,7 @@
       </c>
       <c r="Q47" s="605"/>
       <c r="R47" s="606"/>
-      <c r="S47" s="653"/>
+      <c r="S47" s="625"/>
       <c r="T47" s="518"/>
       <c r="U47" s="538"/>
       <c r="V47" s="538"/>
@@ -41400,7 +40374,7 @@
       </c>
       <c r="Q48" s="605"/>
       <c r="R48" s="606"/>
-      <c r="S48" s="653"/>
+      <c r="S48" s="625"/>
       <c r="T48" s="518"/>
       <c r="U48" s="538"/>
       <c r="V48" s="538"/>
@@ -41429,7 +40403,7 @@
       </c>
       <c r="Q49" s="605"/>
       <c r="R49" s="606"/>
-      <c r="S49" s="653"/>
+      <c r="S49" s="625"/>
       <c r="T49" s="518"/>
       <c r="U49" s="538"/>
       <c r="V49" s="538"/>
@@ -41458,7 +40432,7 @@
       </c>
       <c r="Q50" s="605"/>
       <c r="R50" s="606"/>
-      <c r="S50" s="653"/>
+      <c r="S50" s="625"/>
       <c r="T50" s="518"/>
       <c r="U50" s="538"/>
       <c r="V50" s="538"/>
@@ -41487,7 +40461,7 @@
       </c>
       <c r="Q51" s="605"/>
       <c r="R51" s="606"/>
-      <c r="S51" s="653"/>
+      <c r="S51" s="625"/>
       <c r="T51" s="518"/>
       <c r="U51" s="538"/>
       <c r="V51" s="538"/>
@@ -41516,7 +40490,7 @@
       </c>
       <c r="Q52" s="605"/>
       <c r="R52" s="606"/>
-      <c r="S52" s="653"/>
+      <c r="S52" s="625"/>
       <c r="T52" s="518"/>
       <c r="U52" s="538"/>
       <c r="V52" s="538"/>
@@ -41545,7 +40519,7 @@
       </c>
       <c r="Q53" s="605"/>
       <c r="R53" s="606"/>
-      <c r="S53" s="653"/>
+      <c r="S53" s="625"/>
       <c r="T53" s="518"/>
       <c r="U53" s="538"/>
       <c r="V53" s="538"/>
@@ -41574,7 +40548,7 @@
       </c>
       <c r="Q54" s="605"/>
       <c r="R54" s="606"/>
-      <c r="S54" s="653"/>
+      <c r="S54" s="625"/>
       <c r="T54" s="518"/>
       <c r="U54" s="538"/>
       <c r="V54" s="538"/>
@@ -41603,7 +40577,7 @@
       </c>
       <c r="Q55" s="605"/>
       <c r="R55" s="606"/>
-      <c r="S55" s="653"/>
+      <c r="S55" s="625"/>
       <c r="T55" s="518"/>
       <c r="U55" s="538"/>
       <c r="V55" s="538"/>
@@ -41632,7 +40606,7 @@
       </c>
       <c r="Q56" s="605"/>
       <c r="R56" s="606"/>
-      <c r="S56" s="653"/>
+      <c r="S56" s="625"/>
       <c r="T56" s="518"/>
       <c r="U56" s="538"/>
       <c r="V56" s="538"/>
@@ -41661,7 +40635,7 @@
       </c>
       <c r="Q57" s="605"/>
       <c r="R57" s="606"/>
-      <c r="S57" s="653"/>
+      <c r="S57" s="625"/>
       <c r="T57" s="518"/>
       <c r="U57" s="538"/>
       <c r="V57" s="538"/>
@@ -41690,7 +40664,7 @@
       </c>
       <c r="Q58" s="605"/>
       <c r="R58" s="606"/>
-      <c r="S58" s="653"/>
+      <c r="S58" s="625"/>
       <c r="T58" s="518"/>
       <c r="U58" s="538"/>
       <c r="V58" s="538"/>
@@ -41719,7 +40693,7 @@
       </c>
       <c r="Q59" s="605"/>
       <c r="R59" s="606"/>
-      <c r="S59" s="653"/>
+      <c r="S59" s="625"/>
       <c r="T59" s="518"/>
       <c r="U59" s="538"/>
       <c r="V59" s="538"/>
@@ -41748,7 +40722,7 @@
       </c>
       <c r="Q60" s="605"/>
       <c r="R60" s="606"/>
-      <c r="S60" s="653"/>
+      <c r="S60" s="625"/>
       <c r="T60" s="518"/>
       <c r="U60" s="538"/>
       <c r="V60" s="538"/>
@@ -41777,7 +40751,7 @@
       </c>
       <c r="Q61" s="605"/>
       <c r="R61" s="606"/>
-      <c r="S61" s="653"/>
+      <c r="S61" s="625"/>
       <c r="T61" s="518"/>
       <c r="U61" s="538"/>
       <c r="V61" s="538"/>
@@ -41806,7 +40780,7 @@
       </c>
       <c r="Q62" s="605"/>
       <c r="R62" s="606"/>
-      <c r="S62" s="653"/>
+      <c r="S62" s="625"/>
       <c r="T62" s="518"/>
       <c r="U62" s="538"/>
       <c r="V62" s="538"/>
@@ -41835,7 +40809,7 @@
       </c>
       <c r="Q63" s="605"/>
       <c r="R63" s="606"/>
-      <c r="S63" s="653"/>
+      <c r="S63" s="625"/>
       <c r="T63" s="518"/>
       <c r="U63" s="538"/>
       <c r="V63" s="538"/>
@@ -41864,7 +40838,7 @@
       </c>
       <c r="Q64" s="605"/>
       <c r="R64" s="606"/>
-      <c r="S64" s="653"/>
+      <c r="S64" s="625"/>
       <c r="T64" s="518"/>
       <c r="U64" s="538"/>
       <c r="V64" s="538"/>
@@ -41893,7 +40867,7 @@
       </c>
       <c r="Q65" s="605"/>
       <c r="R65" s="606"/>
-      <c r="S65" s="653"/>
+      <c r="S65" s="625"/>
       <c r="T65" s="518"/>
       <c r="U65" s="538"/>
       <c r="V65" s="538"/>
@@ -41922,7 +40896,7 @@
       </c>
       <c r="Q66" s="605"/>
       <c r="R66" s="606"/>
-      <c r="S66" s="653"/>
+      <c r="S66" s="625"/>
       <c r="T66" s="518"/>
       <c r="U66" s="538"/>
       <c r="V66" s="538"/>
@@ -41951,7 +40925,7 @@
       </c>
       <c r="Q67" s="605"/>
       <c r="R67" s="606"/>
-      <c r="S67" s="653"/>
+      <c r="S67" s="625"/>
       <c r="T67" s="518"/>
       <c r="U67" s="538"/>
       <c r="V67" s="538"/>
@@ -41980,7 +40954,7 @@
       </c>
       <c r="Q68" s="605"/>
       <c r="R68" s="606"/>
-      <c r="S68" s="653"/>
+      <c r="S68" s="625"/>
       <c r="T68" s="518"/>
       <c r="U68" s="538"/>
       <c r="V68" s="538"/>
@@ -42009,7 +40983,7 @@
       </c>
       <c r="Q69" s="605"/>
       <c r="R69" s="606"/>
-      <c r="S69" s="653"/>
+      <c r="S69" s="625"/>
       <c r="T69" s="518"/>
       <c r="U69" s="538"/>
       <c r="V69" s="538"/>
@@ -42038,7 +41012,7 @@
       </c>
       <c r="Q70" s="605"/>
       <c r="R70" s="606"/>
-      <c r="S70" s="653"/>
+      <c r="S70" s="625"/>
       <c r="T70" s="518"/>
       <c r="U70" s="538"/>
       <c r="V70" s="538"/>
@@ -42067,7 +41041,7 @@
       </c>
       <c r="Q71" s="605"/>
       <c r="R71" s="606"/>
-      <c r="S71" s="653"/>
+      <c r="S71" s="625"/>
       <c r="T71" s="518"/>
       <c r="U71" s="538"/>
       <c r="V71" s="538"/>
@@ -42096,7 +41070,7 @@
       </c>
       <c r="Q72" s="605"/>
       <c r="R72" s="606"/>
-      <c r="S72" s="653"/>
+      <c r="S72" s="625"/>
       <c r="T72" s="518"/>
       <c r="U72" s="538"/>
       <c r="V72" s="538"/>
@@ -42125,7 +41099,7 @@
       </c>
       <c r="Q73" s="605"/>
       <c r="R73" s="606"/>
-      <c r="S73" s="653"/>
+      <c r="S73" s="625"/>
       <c r="T73" s="518"/>
       <c r="U73" s="538"/>
       <c r="V73" s="538"/>
@@ -42154,7 +41128,7 @@
       </c>
       <c r="Q74" s="605"/>
       <c r="R74" s="606"/>
-      <c r="S74" s="653"/>
+      <c r="S74" s="625"/>
       <c r="T74" s="518"/>
       <c r="U74" s="538"/>
       <c r="V74" s="538"/>
@@ -42183,7 +41157,7 @@
       </c>
       <c r="Q75" s="605"/>
       <c r="R75" s="606"/>
-      <c r="S75" s="653"/>
+      <c r="S75" s="625"/>
       <c r="T75" s="518"/>
       <c r="U75" s="538"/>
       <c r="V75" s="538"/>
@@ -42212,7 +41186,7 @@
       </c>
       <c r="Q76" s="605"/>
       <c r="R76" s="606"/>
-      <c r="S76" s="653"/>
+      <c r="S76" s="625"/>
       <c r="T76" s="518"/>
       <c r="U76" s="538"/>
       <c r="V76" s="538"/>
@@ -42241,7 +41215,7 @@
       </c>
       <c r="Q77" s="605"/>
       <c r="R77" s="606"/>
-      <c r="S77" s="653"/>
+      <c r="S77" s="625"/>
       <c r="T77" s="518"/>
       <c r="U77" s="538"/>
       <c r="V77" s="538"/>
@@ -42270,7 +41244,7 @@
       </c>
       <c r="Q78" s="605"/>
       <c r="R78" s="606"/>
-      <c r="S78" s="653"/>
+      <c r="S78" s="625"/>
       <c r="T78" s="518"/>
       <c r="U78" s="538"/>
       <c r="V78" s="538"/>
@@ -42299,7 +41273,7 @@
       </c>
       <c r="Q79" s="605"/>
       <c r="R79" s="606"/>
-      <c r="S79" s="653"/>
+      <c r="S79" s="625"/>
       <c r="T79" s="518"/>
       <c r="U79" s="538"/>
       <c r="V79" s="538"/>
@@ -42328,7 +41302,7 @@
       </c>
       <c r="Q80" s="605"/>
       <c r="R80" s="606"/>
-      <c r="S80" s="653"/>
+      <c r="S80" s="625"/>
       <c r="T80" s="518"/>
       <c r="U80" s="538"/>
       <c r="V80" s="538"/>
@@ -42357,7 +41331,7 @@
       </c>
       <c r="Q81" s="605"/>
       <c r="R81" s="606"/>
-      <c r="S81" s="653"/>
+      <c r="S81" s="625"/>
       <c r="T81" s="518"/>
       <c r="U81" s="538"/>
       <c r="V81" s="538"/>
@@ -42386,7 +41360,7 @@
       </c>
       <c r="Q82" s="605"/>
       <c r="R82" s="606"/>
-      <c r="S82" s="653"/>
+      <c r="S82" s="625"/>
       <c r="T82" s="518"/>
       <c r="U82" s="538"/>
       <c r="V82" s="538"/>
@@ -42415,7 +41389,7 @@
       </c>
       <c r="Q83" s="605"/>
       <c r="R83" s="606"/>
-      <c r="S83" s="653"/>
+      <c r="S83" s="625"/>
       <c r="T83" s="518"/>
       <c r="U83" s="538"/>
       <c r="V83" s="538"/>
@@ -42444,7 +41418,7 @@
       </c>
       <c r="Q84" s="605"/>
       <c r="R84" s="606"/>
-      <c r="S84" s="653"/>
+      <c r="S84" s="625"/>
       <c r="T84" s="518"/>
       <c r="U84" s="538"/>
       <c r="V84" s="538"/>
@@ -42473,7 +41447,7 @@
       </c>
       <c r="Q85" s="605"/>
       <c r="R85" s="606"/>
-      <c r="S85" s="653"/>
+      <c r="S85" s="625"/>
       <c r="T85" s="518"/>
       <c r="U85" s="538"/>
       <c r="V85" s="538"/>
@@ -42502,7 +41476,7 @@
       </c>
       <c r="Q86" s="605"/>
       <c r="R86" s="606"/>
-      <c r="S86" s="653"/>
+      <c r="S86" s="625"/>
       <c r="T86" s="518"/>
       <c r="U86" s="538"/>
       <c r="V86" s="538"/>
@@ -42531,7 +41505,7 @@
       </c>
       <c r="Q87" s="605"/>
       <c r="R87" s="606"/>
-      <c r="S87" s="653"/>
+      <c r="S87" s="625"/>
       <c r="T87" s="518"/>
       <c r="U87" s="538"/>
       <c r="V87" s="538"/>
@@ -42560,7 +41534,7 @@
       </c>
       <c r="Q88" s="605"/>
       <c r="R88" s="606"/>
-      <c r="S88" s="653"/>
+      <c r="S88" s="625"/>
       <c r="T88" s="518"/>
       <c r="U88" s="538"/>
       <c r="V88" s="538"/>
@@ -42589,7 +41563,7 @@
       </c>
       <c r="Q89" s="605"/>
       <c r="R89" s="606"/>
-      <c r="S89" s="653"/>
+      <c r="S89" s="625"/>
       <c r="T89" s="518"/>
       <c r="U89" s="538"/>
       <c r="V89" s="538"/>
@@ -42618,7 +41592,7 @@
       </c>
       <c r="Q90" s="605"/>
       <c r="R90" s="606"/>
-      <c r="S90" s="653"/>
+      <c r="S90" s="625"/>
       <c r="T90" s="518"/>
       <c r="U90" s="538"/>
       <c r="V90" s="538"/>
@@ -42647,7 +41621,7 @@
       </c>
       <c r="Q91" s="605"/>
       <c r="R91" s="606"/>
-      <c r="S91" s="653"/>
+      <c r="S91" s="625"/>
       <c r="T91" s="518"/>
       <c r="U91" s="538"/>
       <c r="V91" s="538"/>
@@ -42676,7 +41650,7 @@
       </c>
       <c r="Q92" s="605"/>
       <c r="R92" s="606"/>
-      <c r="S92" s="653"/>
+      <c r="S92" s="625"/>
       <c r="T92" s="518"/>
       <c r="U92" s="538"/>
       <c r="V92" s="538"/>
@@ -42705,7 +41679,7 @@
       </c>
       <c r="Q93" s="605"/>
       <c r="R93" s="606"/>
-      <c r="S93" s="653"/>
+      <c r="S93" s="625"/>
       <c r="T93" s="518"/>
       <c r="U93" s="538"/>
       <c r="V93" s="538"/>
@@ -42734,7 +41708,7 @@
       </c>
       <c r="Q94" s="605"/>
       <c r="R94" s="606"/>
-      <c r="S94" s="653"/>
+      <c r="S94" s="625"/>
       <c r="T94" s="518"/>
       <c r="U94" s="538"/>
       <c r="V94" s="538"/>
@@ -42763,7 +41737,7 @@
       </c>
       <c r="Q95" s="605"/>
       <c r="R95" s="606"/>
-      <c r="S95" s="653"/>
+      <c r="S95" s="625"/>
       <c r="T95" s="518"/>
       <c r="U95" s="538"/>
       <c r="V95" s="538"/>
@@ -42792,7 +41766,7 @@
       </c>
       <c r="Q96" s="605"/>
       <c r="R96" s="606"/>
-      <c r="S96" s="653"/>
+      <c r="S96" s="625"/>
       <c r="T96" s="518"/>
       <c r="U96" s="538"/>
       <c r="V96" s="538"/>
@@ -42821,7 +41795,7 @@
       </c>
       <c r="Q97" s="605"/>
       <c r="R97" s="606"/>
-      <c r="S97" s="653"/>
+      <c r="S97" s="625"/>
       <c r="T97" s="518"/>
       <c r="U97" s="538"/>
       <c r="V97" s="538"/>
@@ -42850,7 +41824,7 @@
       </c>
       <c r="Q98" s="605"/>
       <c r="R98" s="606"/>
-      <c r="S98" s="653"/>
+      <c r="S98" s="625"/>
       <c r="T98" s="518"/>
       <c r="U98" s="538"/>
       <c r="V98" s="538"/>
@@ -42879,7 +41853,7 @@
       </c>
       <c r="Q99" s="605"/>
       <c r="R99" s="606"/>
-      <c r="S99" s="653"/>
+      <c r="S99" s="625"/>
       <c r="T99" s="518"/>
       <c r="U99" s="538"/>
       <c r="V99" s="538"/>
@@ -42908,7 +41882,7 @@
       </c>
       <c r="Q100" s="605"/>
       <c r="R100" s="606"/>
-      <c r="S100" s="653"/>
+      <c r="S100" s="625"/>
       <c r="T100" s="518"/>
       <c r="U100" s="538"/>
       <c r="V100" s="538"/>
@@ -42937,7 +41911,7 @@
       </c>
       <c r="Q101" s="605"/>
       <c r="R101" s="606"/>
-      <c r="S101" s="653"/>
+      <c r="S101" s="625"/>
       <c r="T101" s="518"/>
       <c r="U101" s="538"/>
       <c r="V101" s="538"/>
@@ -42966,7 +41940,7 @@
       </c>
       <c r="Q102" s="605"/>
       <c r="R102" s="606"/>
-      <c r="S102" s="653"/>
+      <c r="S102" s="625"/>
       <c r="T102" s="518"/>
       <c r="U102" s="538"/>
       <c r="V102" s="538"/>
@@ -42995,7 +41969,7 @@
       </c>
       <c r="Q103" s="605"/>
       <c r="R103" s="606"/>
-      <c r="S103" s="653"/>
+      <c r="S103" s="625"/>
       <c r="T103" s="518"/>
       <c r="U103" s="538"/>
       <c r="V103" s="538"/>
@@ -43024,7 +41998,7 @@
       </c>
       <c r="Q104" s="605"/>
       <c r="R104" s="606"/>
-      <c r="S104" s="653"/>
+      <c r="S104" s="625"/>
       <c r="T104" s="518"/>
       <c r="U104" s="538"/>
       <c r="V104" s="538"/>
@@ -43053,7 +42027,7 @@
       </c>
       <c r="Q105" s="605"/>
       <c r="R105" s="606"/>
-      <c r="S105" s="653"/>
+      <c r="S105" s="625"/>
       <c r="T105" s="518"/>
       <c r="U105" s="538"/>
       <c r="V105" s="538"/>
@@ -43082,7 +42056,7 @@
       </c>
       <c r="Q106" s="605"/>
       <c r="R106" s="606"/>
-      <c r="S106" s="653"/>
+      <c r="S106" s="625"/>
       <c r="T106" s="518"/>
       <c r="U106" s="538"/>
       <c r="V106" s="538"/>
@@ -43111,7 +42085,7 @@
       </c>
       <c r="Q107" s="605"/>
       <c r="R107" s="606"/>
-      <c r="S107" s="653"/>
+      <c r="S107" s="625"/>
       <c r="T107" s="518"/>
       <c r="U107" s="538"/>
       <c r="V107" s="538"/>
@@ -43140,7 +42114,7 @@
       </c>
       <c r="Q108" s="605"/>
       <c r="R108" s="606"/>
-      <c r="S108" s="653"/>
+      <c r="S108" s="625"/>
       <c r="T108" s="518"/>
       <c r="U108" s="439"/>
       <c r="V108" s="439"/>
@@ -43169,7 +42143,7 @@
       </c>
       <c r="Q109" s="605"/>
       <c r="R109" s="606"/>
-      <c r="S109" s="653"/>
+      <c r="S109" s="625"/>
       <c r="T109" s="518"/>
       <c r="U109" s="538"/>
       <c r="V109" s="538"/>
@@ -43198,7 +42172,7 @@
       </c>
       <c r="Q110" s="605"/>
       <c r="R110" s="606"/>
-      <c r="S110" s="653"/>
+      <c r="S110" s="625"/>
       <c r="T110" s="518"/>
       <c r="U110" s="538"/>
       <c r="V110" s="538"/>
@@ -43227,7 +42201,7 @@
       </c>
       <c r="Q111" s="605"/>
       <c r="R111" s="606"/>
-      <c r="S111" s="653"/>
+      <c r="S111" s="625"/>
       <c r="T111" s="518"/>
       <c r="U111" s="538"/>
       <c r="V111" s="538"/>
@@ -43256,7 +42230,7 @@
       </c>
       <c r="Q112" s="605"/>
       <c r="R112" s="606"/>
-      <c r="S112" s="653"/>
+      <c r="S112" s="625"/>
       <c r="T112" s="518"/>
       <c r="U112" s="538"/>
       <c r="V112" s="538"/>
@@ -43285,7 +42259,7 @@
       </c>
       <c r="Q113" s="605"/>
       <c r="R113" s="606"/>
-      <c r="S113" s="653"/>
+      <c r="S113" s="625"/>
       <c r="T113" s="518"/>
       <c r="U113" s="538"/>
       <c r="V113" s="538"/>
@@ -43314,7 +42288,7 @@
       </c>
       <c r="Q114" s="605"/>
       <c r="R114" s="606"/>
-      <c r="S114" s="653"/>
+      <c r="S114" s="625"/>
       <c r="T114" s="518"/>
       <c r="U114" s="538"/>
       <c r="V114" s="538"/>
@@ -43343,7 +42317,7 @@
       </c>
       <c r="Q115" s="605"/>
       <c r="R115" s="606"/>
-      <c r="S115" s="653"/>
+      <c r="S115" s="625"/>
       <c r="T115" s="518"/>
       <c r="U115" s="538"/>
       <c r="V115" s="538"/>
@@ -43372,7 +42346,7 @@
       </c>
       <c r="Q116" s="605"/>
       <c r="R116" s="606"/>
-      <c r="S116" s="653"/>
+      <c r="S116" s="625"/>
       <c r="T116" s="518"/>
       <c r="U116" s="439"/>
       <c r="V116" s="439"/>
@@ -43401,7 +42375,7 @@
       </c>
       <c r="Q117" s="605"/>
       <c r="R117" s="606"/>
-      <c r="S117" s="653"/>
+      <c r="S117" s="625"/>
       <c r="T117" s="518"/>
       <c r="U117" s="538"/>
       <c r="V117" s="538"/>
@@ -43430,7 +42404,7 @@
       </c>
       <c r="Q118" s="605"/>
       <c r="R118" s="606"/>
-      <c r="S118" s="653"/>
+      <c r="S118" s="625"/>
       <c r="T118" s="518"/>
       <c r="U118" s="538"/>
       <c r="V118" s="538"/>
@@ -43459,7 +42433,7 @@
       </c>
       <c r="Q119" s="605"/>
       <c r="R119" s="606"/>
-      <c r="S119" s="653"/>
+      <c r="S119" s="625"/>
       <c r="T119" s="518"/>
       <c r="U119" s="538"/>
       <c r="V119" s="538"/>
@@ -43488,7 +42462,7 @@
       </c>
       <c r="Q120" s="605"/>
       <c r="R120" s="606"/>
-      <c r="S120" s="653"/>
+      <c r="S120" s="625"/>
       <c r="T120" s="518"/>
       <c r="U120" s="538"/>
       <c r="V120" s="538"/>
@@ -43517,7 +42491,7 @@
       </c>
       <c r="Q121" s="605"/>
       <c r="R121" s="606"/>
-      <c r="S121" s="653"/>
+      <c r="S121" s="625"/>
       <c r="T121" s="518"/>
       <c r="U121" s="538"/>
       <c r="V121" s="538"/>
@@ -43546,7 +42520,7 @@
       </c>
       <c r="Q122" s="605"/>
       <c r="R122" s="606"/>
-      <c r="S122" s="653"/>
+      <c r="S122" s="625"/>
       <c r="T122" s="518"/>
       <c r="U122" s="538"/>
       <c r="V122" s="538"/>
@@ -43575,7 +42549,7 @@
       </c>
       <c r="Q123" s="605"/>
       <c r="R123" s="606"/>
-      <c r="S123" s="653"/>
+      <c r="S123" s="625"/>
       <c r="T123" s="518"/>
       <c r="U123" s="538"/>
       <c r="V123" s="538"/>
@@ -43604,7 +42578,7 @@
       </c>
       <c r="Q124" s="605"/>
       <c r="R124" s="606"/>
-      <c r="S124" s="653"/>
+      <c r="S124" s="625"/>
       <c r="T124" s="518"/>
       <c r="U124" s="439"/>
       <c r="V124" s="439"/>
@@ -43633,7 +42607,7 @@
       </c>
       <c r="Q125" s="605"/>
       <c r="R125" s="606"/>
-      <c r="S125" s="653"/>
+      <c r="S125" s="625"/>
       <c r="T125" s="518"/>
       <c r="U125" s="538"/>
       <c r="V125" s="538"/>
@@ -43662,7 +42636,7 @@
       </c>
       <c r="Q126" s="605"/>
       <c r="R126" s="606"/>
-      <c r="S126" s="653"/>
+      <c r="S126" s="625"/>
       <c r="T126" s="518"/>
       <c r="U126" s="538"/>
       <c r="V126" s="538"/>
@@ -43691,7 +42665,7 @@
       </c>
       <c r="Q127" s="605"/>
       <c r="R127" s="606"/>
-      <c r="S127" s="653"/>
+      <c r="S127" s="625"/>
       <c r="T127" s="518"/>
       <c r="U127" s="538"/>
       <c r="V127" s="538"/>
@@ -43720,7 +42694,7 @@
       </c>
       <c r="Q128" s="605"/>
       <c r="R128" s="606"/>
-      <c r="S128" s="653"/>
+      <c r="S128" s="625"/>
       <c r="T128" s="518"/>
       <c r="U128" s="538"/>
       <c r="V128" s="538"/>
@@ -43749,7 +42723,7 @@
       </c>
       <c r="Q129" s="605"/>
       <c r="R129" s="606"/>
-      <c r="S129" s="653"/>
+      <c r="S129" s="625"/>
       <c r="T129" s="518"/>
       <c r="U129" s="538"/>
       <c r="V129" s="538"/>
@@ -43778,7 +42752,7 @@
       </c>
       <c r="Q130" s="605"/>
       <c r="R130" s="606"/>
-      <c r="S130" s="653"/>
+      <c r="S130" s="625"/>
       <c r="T130" s="518"/>
       <c r="U130" s="538"/>
       <c r="V130" s="538"/>
@@ -43807,7 +42781,7 @@
       </c>
       <c r="Q131" s="605"/>
       <c r="R131" s="606"/>
-      <c r="S131" s="653"/>
+      <c r="S131" s="625"/>
       <c r="T131" s="518"/>
       <c r="U131" s="538"/>
       <c r="V131" s="538"/>
@@ -43836,7 +42810,7 @@
       </c>
       <c r="Q132" s="605"/>
       <c r="R132" s="606"/>
-      <c r="S132" s="653"/>
+      <c r="S132" s="625"/>
       <c r="T132" s="518"/>
       <c r="U132" s="538"/>
       <c r="V132" s="538"/>
@@ -43865,7 +42839,7 @@
       </c>
       <c r="Q133" s="605"/>
       <c r="R133" s="606"/>
-      <c r="S133" s="653"/>
+      <c r="S133" s="625"/>
       <c r="T133" s="518"/>
       <c r="U133" s="538"/>
       <c r="V133" s="538"/>
@@ -43894,7 +42868,7 @@
       </c>
       <c r="Q134" s="605"/>
       <c r="R134" s="606"/>
-      <c r="S134" s="653"/>
+      <c r="S134" s="625"/>
       <c r="T134" s="518"/>
       <c r="U134" s="538"/>
       <c r="V134" s="538"/>
@@ -43923,7 +42897,7 @@
       </c>
       <c r="Q135" s="605"/>
       <c r="R135" s="606"/>
-      <c r="S135" s="653"/>
+      <c r="S135" s="625"/>
       <c r="T135" s="518"/>
       <c r="U135" s="439"/>
       <c r="V135" s="439"/>
@@ -43952,7 +42926,7 @@
       </c>
       <c r="Q136" s="605"/>
       <c r="R136" s="606"/>
-      <c r="S136" s="653"/>
+      <c r="S136" s="625"/>
       <c r="T136" s="518"/>
       <c r="U136" s="538"/>
       <c r="V136" s="538"/>
@@ -43981,7 +42955,7 @@
       </c>
       <c r="Q137" s="605"/>
       <c r="R137" s="606"/>
-      <c r="S137" s="653"/>
+      <c r="S137" s="625"/>
       <c r="T137" s="518"/>
       <c r="U137" s="538"/>
       <c r="V137" s="538"/>
@@ -44010,7 +42984,7 @@
       </c>
       <c r="Q138" s="605"/>
       <c r="R138" s="606"/>
-      <c r="S138" s="653"/>
+      <c r="S138" s="625"/>
       <c r="T138" s="518"/>
       <c r="U138" s="538"/>
       <c r="V138" s="538"/>
@@ -44039,7 +43013,7 @@
       </c>
       <c r="Q139" s="605"/>
       <c r="R139" s="606"/>
-      <c r="S139" s="653"/>
+      <c r="S139" s="625"/>
       <c r="T139" s="518"/>
       <c r="U139" s="538"/>
       <c r="V139" s="538"/>
@@ -44068,7 +43042,7 @@
       </c>
       <c r="Q140" s="605"/>
       <c r="R140" s="606"/>
-      <c r="S140" s="653"/>
+      <c r="S140" s="625"/>
       <c r="T140" s="518"/>
       <c r="U140" s="538"/>
       <c r="V140" s="538"/>
@@ -44097,7 +43071,7 @@
       </c>
       <c r="Q141" s="605"/>
       <c r="R141" s="606"/>
-      <c r="S141" s="653"/>
+      <c r="S141" s="625"/>
       <c r="T141" s="518"/>
       <c r="U141" s="538"/>
       <c r="V141" s="538"/>
@@ -44126,7 +43100,7 @@
       </c>
       <c r="Q142" s="605"/>
       <c r="R142" s="606"/>
-      <c r="S142" s="653"/>
+      <c r="S142" s="625"/>
       <c r="T142" s="518"/>
       <c r="U142" s="538"/>
       <c r="V142" s="538"/>
@@ -44155,7 +43129,7 @@
       </c>
       <c r="Q143" s="605"/>
       <c r="R143" s="606"/>
-      <c r="S143" s="653"/>
+      <c r="S143" s="625"/>
       <c r="T143" s="518"/>
       <c r="U143" s="439"/>
       <c r="V143" s="439"/>
@@ -44184,7 +43158,7 @@
       </c>
       <c r="Q144" s="605"/>
       <c r="R144" s="606"/>
-      <c r="S144" s="653"/>
+      <c r="S144" s="625"/>
       <c r="T144" s="518"/>
       <c r="U144" s="538"/>
       <c r="V144" s="538"/>
@@ -44213,7 +43187,7 @@
       </c>
       <c r="Q145" s="605"/>
       <c r="R145" s="606"/>
-      <c r="S145" s="653"/>
+      <c r="S145" s="625"/>
       <c r="T145" s="518"/>
       <c r="U145" s="538"/>
       <c r="V145" s="538"/>
@@ -44242,7 +43216,7 @@
       </c>
       <c r="Q146" s="605"/>
       <c r="R146" s="606"/>
-      <c r="S146" s="653"/>
+      <c r="S146" s="625"/>
       <c r="T146" s="518"/>
       <c r="U146" s="538"/>
       <c r="V146" s="538"/>
@@ -44271,7 +43245,7 @@
       </c>
       <c r="Q147" s="605"/>
       <c r="R147" s="606"/>
-      <c r="S147" s="653"/>
+      <c r="S147" s="625"/>
       <c r="T147" s="518"/>
       <c r="U147" s="538"/>
       <c r="V147" s="538"/>
@@ -44300,7 +43274,7 @@
       </c>
       <c r="Q148" s="605"/>
       <c r="R148" s="606"/>
-      <c r="S148" s="653"/>
+      <c r="S148" s="625"/>
       <c r="T148" s="518"/>
       <c r="U148" s="538"/>
       <c r="V148" s="538"/>
@@ -44329,7 +43303,7 @@
       </c>
       <c r="Q149" s="605"/>
       <c r="R149" s="606"/>
-      <c r="S149" s="653"/>
+      <c r="S149" s="625"/>
       <c r="T149" s="518"/>
       <c r="U149" s="538"/>
       <c r="V149" s="538"/>
@@ -44358,7 +43332,7 @@
       </c>
       <c r="Q150" s="605"/>
       <c r="R150" s="606"/>
-      <c r="S150" s="653"/>
+      <c r="S150" s="625"/>
       <c r="T150" s="518"/>
       <c r="U150" s="538"/>
       <c r="V150" s="538"/>
@@ -44387,7 +43361,7 @@
       </c>
       <c r="Q151" s="605"/>
       <c r="R151" s="606"/>
-      <c r="S151" s="653"/>
+      <c r="S151" s="625"/>
       <c r="T151" s="518"/>
       <c r="U151" s="439"/>
       <c r="V151" s="439"/>
@@ -44416,7 +43390,7 @@
       </c>
       <c r="Q152" s="605"/>
       <c r="R152" s="606"/>
-      <c r="S152" s="653"/>
+      <c r="S152" s="625"/>
       <c r="T152" s="518"/>
       <c r="U152" s="538"/>
       <c r="V152" s="538"/>
@@ -44445,7 +43419,7 @@
       </c>
       <c r="Q153" s="605"/>
       <c r="R153" s="606"/>
-      <c r="S153" s="653"/>
+      <c r="S153" s="625"/>
       <c r="T153" s="518"/>
       <c r="U153" s="538"/>
       <c r="V153" s="538"/>
@@ -44474,7 +43448,7 @@
       </c>
       <c r="Q154" s="605"/>
       <c r="R154" s="606"/>
-      <c r="S154" s="653"/>
+      <c r="S154" s="625"/>
       <c r="T154" s="518"/>
       <c r="U154" s="538"/>
       <c r="V154" s="538"/>
@@ -44503,7 +43477,7 @@
       </c>
       <c r="Q155" s="605"/>
       <c r="R155" s="606"/>
-      <c r="S155" s="653"/>
+      <c r="S155" s="625"/>
       <c r="T155" s="518"/>
       <c r="U155" s="538"/>
       <c r="V155" s="538"/>
@@ -44532,7 +43506,7 @@
       </c>
       <c r="Q156" s="605"/>
       <c r="R156" s="606"/>
-      <c r="S156" s="653"/>
+      <c r="S156" s="625"/>
       <c r="T156" s="518"/>
       <c r="U156" s="538"/>
       <c r="V156" s="538"/>
@@ -44561,7 +43535,7 @@
       </c>
       <c r="Q157" s="605"/>
       <c r="R157" s="606"/>
-      <c r="S157" s="653"/>
+      <c r="S157" s="625"/>
       <c r="T157" s="518"/>
       <c r="U157" s="538"/>
       <c r="V157" s="538"/>
@@ -44590,7 +43564,7 @@
       </c>
       <c r="Q158" s="605"/>
       <c r="R158" s="606"/>
-      <c r="S158" s="653"/>
+      <c r="S158" s="625"/>
       <c r="T158" s="518"/>
       <c r="U158" s="538"/>
       <c r="V158" s="538"/>
@@ -44619,7 +43593,7 @@
       </c>
       <c r="Q159" s="605"/>
       <c r="R159" s="606"/>
-      <c r="S159" s="653"/>
+      <c r="S159" s="625"/>
       <c r="T159" s="518"/>
       <c r="U159" s="538"/>
       <c r="V159" s="538"/>
@@ -44648,7 +43622,7 @@
       </c>
       <c r="Q160" s="605"/>
       <c r="R160" s="606"/>
-      <c r="S160" s="653"/>
+      <c r="S160" s="625"/>
       <c r="T160" s="518"/>
       <c r="U160" s="538"/>
       <c r="V160" s="538"/>
@@ -44677,7 +43651,7 @@
       </c>
       <c r="Q161" s="605"/>
       <c r="R161" s="606"/>
-      <c r="S161" s="653"/>
+      <c r="S161" s="625"/>
       <c r="T161" s="518"/>
       <c r="U161" s="538"/>
       <c r="V161" s="538"/>
@@ -44706,7 +43680,7 @@
       </c>
       <c r="Q162" s="605"/>
       <c r="R162" s="606"/>
-      <c r="S162" s="653"/>
+      <c r="S162" s="625"/>
       <c r="T162" s="518"/>
       <c r="U162" s="439"/>
       <c r="V162" s="439"/>
@@ -44735,7 +43709,7 @@
       </c>
       <c r="Q163" s="605"/>
       <c r="R163" s="606"/>
-      <c r="S163" s="653"/>
+      <c r="S163" s="625"/>
       <c r="T163" s="518"/>
       <c r="U163" s="538"/>
       <c r="V163" s="538"/>
@@ -44764,7 +43738,7 @@
       </c>
       <c r="Q164" s="605"/>
       <c r="R164" s="606"/>
-      <c r="S164" s="653"/>
+      <c r="S164" s="625"/>
       <c r="T164" s="518"/>
       <c r="U164" s="538"/>
       <c r="V164" s="538"/>
@@ -44793,7 +43767,7 @@
       </c>
       <c r="Q165" s="605"/>
       <c r="R165" s="606"/>
-      <c r="S165" s="653"/>
+      <c r="S165" s="625"/>
       <c r="T165" s="518"/>
       <c r="U165" s="538"/>
       <c r="V165" s="538"/>
@@ -44822,7 +43796,7 @@
       </c>
       <c r="Q166" s="605"/>
       <c r="R166" s="606"/>
-      <c r="S166" s="653"/>
+      <c r="S166" s="625"/>
       <c r="T166" s="518"/>
       <c r="U166" s="538"/>
       <c r="V166" s="538"/>
@@ -44851,7 +43825,7 @@
       </c>
       <c r="Q167" s="605"/>
       <c r="R167" s="606"/>
-      <c r="S167" s="653"/>
+      <c r="S167" s="625"/>
       <c r="T167" s="518"/>
       <c r="U167" s="538"/>
       <c r="V167" s="538"/>
@@ -44880,7 +43854,7 @@
       </c>
       <c r="Q168" s="605"/>
       <c r="R168" s="606"/>
-      <c r="S168" s="653"/>
+      <c r="S168" s="625"/>
       <c r="T168" s="518"/>
       <c r="U168" s="538"/>
       <c r="V168" s="538"/>
@@ -44909,7 +43883,7 @@
       </c>
       <c r="Q169" s="605"/>
       <c r="R169" s="606"/>
-      <c r="S169" s="653"/>
+      <c r="S169" s="625"/>
       <c r="T169" s="518"/>
       <c r="U169" s="538"/>
       <c r="V169" s="538"/>
@@ -44938,7 +43912,7 @@
       </c>
       <c r="Q170" s="605"/>
       <c r="R170" s="606"/>
-      <c r="S170" s="653"/>
+      <c r="S170" s="625"/>
       <c r="T170" s="518"/>
       <c r="U170" s="439"/>
       <c r="V170" s="439"/>
@@ -44967,7 +43941,7 @@
       </c>
       <c r="Q171" s="605"/>
       <c r="R171" s="606"/>
-      <c r="S171" s="653"/>
+      <c r="S171" s="625"/>
       <c r="T171" s="518"/>
       <c r="U171" s="538"/>
       <c r="V171" s="538"/>
@@ -44996,7 +43970,7 @@
       </c>
       <c r="Q172" s="605"/>
       <c r="R172" s="606"/>
-      <c r="S172" s="653"/>
+      <c r="S172" s="625"/>
       <c r="T172" s="518"/>
       <c r="U172" s="538"/>
       <c r="V172" s="538"/>
@@ -45025,7 +43999,7 @@
       </c>
       <c r="Q173" s="605"/>
       <c r="R173" s="606"/>
-      <c r="S173" s="653"/>
+      <c r="S173" s="625"/>
       <c r="T173" s="518"/>
       <c r="U173" s="538"/>
       <c r="V173" s="538"/>
@@ -45054,7 +44028,7 @@
       </c>
       <c r="Q174" s="605"/>
       <c r="R174" s="606"/>
-      <c r="S174" s="653"/>
+      <c r="S174" s="625"/>
       <c r="T174" s="518"/>
       <c r="U174" s="538"/>
       <c r="V174" s="538"/>
@@ -45083,7 +44057,7 @@
       </c>
       <c r="Q175" s="605"/>
       <c r="R175" s="606"/>
-      <c r="S175" s="653"/>
+      <c r="S175" s="625"/>
       <c r="T175" s="518"/>
       <c r="U175" s="538"/>
       <c r="V175" s="538"/>
@@ -45112,7 +44086,7 @@
       </c>
       <c r="Q176" s="605"/>
       <c r="R176" s="606"/>
-      <c r="S176" s="653"/>
+      <c r="S176" s="625"/>
       <c r="T176" s="518"/>
       <c r="U176" s="538"/>
       <c r="V176" s="538"/>
@@ -45141,7 +44115,7 @@
       </c>
       <c r="Q177" s="605"/>
       <c r="R177" s="606"/>
-      <c r="S177" s="653"/>
+      <c r="S177" s="625"/>
       <c r="T177" s="518"/>
       <c r="U177" s="538"/>
       <c r="V177" s="538"/>
@@ -45170,7 +44144,7 @@
       </c>
       <c r="Q178" s="605"/>
       <c r="R178" s="606"/>
-      <c r="S178" s="653"/>
+      <c r="S178" s="625"/>
       <c r="T178" s="518"/>
       <c r="U178" s="439"/>
       <c r="V178" s="439"/>
@@ -45199,7 +44173,7 @@
       </c>
       <c r="Q179" s="605"/>
       <c r="R179" s="606"/>
-      <c r="S179" s="653"/>
+      <c r="S179" s="625"/>
       <c r="T179" s="518"/>
       <c r="U179" s="538"/>
       <c r="V179" s="538"/>
@@ -45228,7 +44202,7 @@
       </c>
       <c r="Q180" s="605"/>
       <c r="R180" s="606"/>
-      <c r="S180" s="653"/>
+      <c r="S180" s="625"/>
       <c r="T180" s="518"/>
       <c r="U180" s="538"/>
       <c r="V180" s="538"/>
@@ -45257,7 +44231,7 @@
       </c>
       <c r="Q181" s="605"/>
       <c r="R181" s="606"/>
-      <c r="S181" s="653"/>
+      <c r="S181" s="625"/>
       <c r="T181" s="518"/>
       <c r="U181" s="538"/>
       <c r="V181" s="538"/>
@@ -45286,7 +44260,7 @@
       </c>
       <c r="Q182" s="605"/>
       <c r="R182" s="606"/>
-      <c r="S182" s="653"/>
+      <c r="S182" s="625"/>
       <c r="T182" s="518"/>
       <c r="U182" s="538"/>
       <c r="V182" s="538"/>
@@ -45315,7 +44289,7 @@
       </c>
       <c r="Q183" s="605"/>
       <c r="R183" s="606"/>
-      <c r="S183" s="653"/>
+      <c r="S183" s="625"/>
       <c r="T183" s="518"/>
       <c r="U183" s="538"/>
       <c r="V183" s="538"/>
@@ -45344,7 +44318,7 @@
       </c>
       <c r="Q184" s="605"/>
       <c r="R184" s="606"/>
-      <c r="S184" s="653"/>
+      <c r="S184" s="625"/>
       <c r="T184" s="518"/>
       <c r="U184" s="538"/>
       <c r="V184" s="538"/>
@@ -45373,7 +44347,7 @@
       </c>
       <c r="Q185" s="605"/>
       <c r="R185" s="606"/>
-      <c r="S185" s="653"/>
+      <c r="S185" s="625"/>
       <c r="T185" s="518"/>
       <c r="U185" s="538"/>
       <c r="V185" s="538"/>
@@ -45402,7 +44376,7 @@
       </c>
       <c r="Q186" s="605"/>
       <c r="R186" s="606"/>
-      <c r="S186" s="653"/>
+      <c r="S186" s="625"/>
       <c r="T186" s="518"/>
       <c r="U186" s="538"/>
       <c r="V186" s="538"/>
@@ -45431,7 +44405,7 @@
       </c>
       <c r="Q187" s="605"/>
       <c r="R187" s="606"/>
-      <c r="S187" s="653"/>
+      <c r="S187" s="625"/>
       <c r="T187" s="518"/>
       <c r="U187" s="538"/>
       <c r="V187" s="538"/>
@@ -45460,7 +44434,7 @@
       </c>
       <c r="Q188" s="605"/>
       <c r="R188" s="606"/>
-      <c r="S188" s="653"/>
+      <c r="S188" s="625"/>
       <c r="T188" s="518"/>
       <c r="U188" s="538"/>
       <c r="V188" s="538"/>
@@ -45489,7 +44463,7 @@
       </c>
       <c r="Q189" s="605"/>
       <c r="R189" s="606"/>
-      <c r="S189" s="653"/>
+      <c r="S189" s="625"/>
       <c r="T189" s="518"/>
       <c r="U189" s="439"/>
       <c r="V189" s="439"/>
@@ -45518,7 +44492,7 @@
       </c>
       <c r="Q190" s="605"/>
       <c r="R190" s="606"/>
-      <c r="S190" s="653"/>
+      <c r="S190" s="625"/>
       <c r="T190" s="518"/>
       <c r="U190" s="538"/>
       <c r="V190" s="538"/>
@@ -45547,7 +44521,7 @@
       </c>
       <c r="Q191" s="605"/>
       <c r="R191" s="606"/>
-      <c r="S191" s="653"/>
+      <c r="S191" s="625"/>
       <c r="T191" s="518"/>
       <c r="U191" s="538"/>
       <c r="V191" s="538"/>
@@ -45576,7 +44550,7 @@
       </c>
       <c r="Q192" s="605"/>
       <c r="R192" s="606"/>
-      <c r="S192" s="653"/>
+      <c r="S192" s="625"/>
       <c r="T192" s="518"/>
       <c r="U192" s="538"/>
       <c r="V192" s="538"/>
@@ -45605,7 +44579,7 @@
       </c>
       <c r="Q193" s="605"/>
       <c r="R193" s="606"/>
-      <c r="S193" s="653"/>
+      <c r="S193" s="625"/>
       <c r="T193" s="518"/>
       <c r="U193" s="538"/>
       <c r="V193" s="538"/>
@@ -45634,7 +44608,7 @@
       </c>
       <c r="Q194" s="605"/>
       <c r="R194" s="606"/>
-      <c r="S194" s="653"/>
+      <c r="S194" s="625"/>
       <c r="T194" s="518"/>
       <c r="U194" s="538"/>
       <c r="V194" s="538"/>
@@ -45663,7 +44637,7 @@
       </c>
       <c r="Q195" s="605"/>
       <c r="R195" s="606"/>
-      <c r="S195" s="653"/>
+      <c r="S195" s="625"/>
       <c r="T195" s="518"/>
       <c r="U195" s="538"/>
       <c r="V195" s="538"/>
@@ -45692,7 +44666,7 @@
       </c>
       <c r="Q196" s="605"/>
       <c r="R196" s="606"/>
-      <c r="S196" s="653"/>
+      <c r="S196" s="625"/>
       <c r="T196" s="518"/>
       <c r="U196" s="538"/>
       <c r="V196" s="538"/>
@@ -45721,7 +44695,7 @@
       </c>
       <c r="Q197" s="605"/>
       <c r="R197" s="606"/>
-      <c r="S197" s="653"/>
+      <c r="S197" s="625"/>
       <c r="T197" s="518"/>
       <c r="U197" s="439"/>
       <c r="V197" s="439"/>
@@ -45750,7 +44724,7 @@
       </c>
       <c r="Q198" s="605"/>
       <c r="R198" s="606"/>
-      <c r="S198" s="653"/>
+      <c r="S198" s="625"/>
       <c r="T198" s="518"/>
       <c r="U198" s="538"/>
       <c r="V198" s="538"/>
@@ -45779,7 +44753,7 @@
       </c>
       <c r="Q199" s="605"/>
       <c r="R199" s="606"/>
-      <c r="S199" s="653"/>
+      <c r="S199" s="625"/>
       <c r="T199" s="518"/>
       <c r="U199" s="538"/>
       <c r="V199" s="538"/>
@@ -45808,7 +44782,7 @@
       </c>
       <c r="Q200" s="605"/>
       <c r="R200" s="606"/>
-      <c r="S200" s="653"/>
+      <c r="S200" s="625"/>
       <c r="T200" s="518"/>
       <c r="U200" s="538"/>
       <c r="V200" s="538"/>
@@ -45837,7 +44811,7 @@
       </c>
       <c r="Q201" s="605"/>
       <c r="R201" s="606"/>
-      <c r="S201" s="653"/>
+      <c r="S201" s="625"/>
       <c r="T201" s="518"/>
       <c r="U201" s="538"/>
       <c r="V201" s="538"/>
@@ -45866,7 +44840,7 @@
       </c>
       <c r="Q202" s="605"/>
       <c r="R202" s="606"/>
-      <c r="S202" s="653"/>
+      <c r="S202" s="625"/>
       <c r="T202" s="518"/>
       <c r="U202" s="538"/>
       <c r="V202" s="538"/>
@@ -45895,7 +44869,7 @@
       </c>
       <c r="Q203" s="605"/>
       <c r="R203" s="606"/>
-      <c r="S203" s="653"/>
+      <c r="S203" s="625"/>
       <c r="T203" s="518"/>
       <c r="U203" s="538"/>
       <c r="V203" s="538"/>
@@ -45924,7 +44898,7 @@
       </c>
       <c r="Q204" s="605"/>
       <c r="R204" s="606"/>
-      <c r="S204" s="653"/>
+      <c r="S204" s="625"/>
       <c r="T204" s="518"/>
       <c r="U204" s="538"/>
       <c r="V204" s="538"/>
@@ -45953,7 +44927,7 @@
       </c>
       <c r="Q205" s="605"/>
       <c r="R205" s="606"/>
-      <c r="S205" s="653"/>
+      <c r="S205" s="625"/>
       <c r="T205" s="518"/>
       <c r="U205" s="439"/>
       <c r="V205" s="439"/>
@@ -45982,7 +44956,7 @@
       </c>
       <c r="Q206" s="605"/>
       <c r="R206" s="606"/>
-      <c r="S206" s="653"/>
+      <c r="S206" s="625"/>
       <c r="T206" s="518"/>
       <c r="U206" s="538"/>
       <c r="V206" s="538"/>
@@ -46011,7 +44985,7 @@
       </c>
       <c r="Q207" s="605"/>
       <c r="R207" s="606"/>
-      <c r="S207" s="653"/>
+      <c r="S207" s="625"/>
       <c r="T207" s="518"/>
       <c r="U207" s="538"/>
       <c r="V207" s="538"/>
@@ -46040,7 +45014,7 @@
       </c>
       <c r="Q208" s="605"/>
       <c r="R208" s="606"/>
-      <c r="S208" s="653"/>
+      <c r="S208" s="625"/>
       <c r="T208" s="518"/>
       <c r="U208" s="538"/>
       <c r="V208" s="538"/>
@@ -46069,7 +45043,7 @@
       </c>
       <c r="Q209" s="605"/>
       <c r="R209" s="606"/>
-      <c r="S209" s="653"/>
+      <c r="S209" s="625"/>
       <c r="T209" s="518"/>
       <c r="U209" s="538"/>
       <c r="V209" s="538"/>
@@ -46098,7 +45072,7 @@
       </c>
       <c r="Q210" s="605"/>
       <c r="R210" s="606"/>
-      <c r="S210" s="653"/>
+      <c r="S210" s="625"/>
       <c r="T210" s="518"/>
       <c r="U210" s="538"/>
       <c r="V210" s="538"/>
@@ -46127,7 +45101,7 @@
       </c>
       <c r="Q211" s="605"/>
       <c r="R211" s="606"/>
-      <c r="S211" s="653"/>
+      <c r="S211" s="625"/>
       <c r="T211" s="518"/>
       <c r="U211" s="538"/>
       <c r="V211" s="538"/>
@@ -46156,7 +45130,7 @@
       </c>
       <c r="Q212" s="605"/>
       <c r="R212" s="606"/>
-      <c r="S212" s="653"/>
+      <c r="S212" s="625"/>
       <c r="T212" s="518"/>
       <c r="U212" s="538"/>
       <c r="V212" s="538"/>
@@ -46185,7 +45159,7 @@
       </c>
       <c r="Q213" s="605"/>
       <c r="R213" s="606"/>
-      <c r="S213" s="653"/>
+      <c r="S213" s="625"/>
       <c r="T213" s="518"/>
       <c r="U213" s="538"/>
       <c r="V213" s="538"/>
@@ -46214,7 +45188,7 @@
       </c>
       <c r="Q214" s="605"/>
       <c r="R214" s="606"/>
-      <c r="S214" s="653"/>
+      <c r="S214" s="625"/>
       <c r="T214" s="518"/>
       <c r="U214" s="538"/>
       <c r="V214" s="538"/>
@@ -46243,7 +45217,7 @@
       </c>
       <c r="Q215" s="605"/>
       <c r="R215" s="606"/>
-      <c r="S215" s="653"/>
+      <c r="S215" s="625"/>
       <c r="T215" s="518"/>
       <c r="U215" s="538"/>
       <c r="V215" s="538"/>
@@ -46272,7 +45246,7 @@
       </c>
       <c r="Q216" s="605"/>
       <c r="R216" s="606"/>
-      <c r="S216" s="653"/>
+      <c r="S216" s="625"/>
       <c r="T216" s="518"/>
       <c r="U216" s="439"/>
       <c r="V216" s="439"/>
@@ -46301,7 +45275,7 @@
       </c>
       <c r="Q217" s="605"/>
       <c r="R217" s="606"/>
-      <c r="S217" s="653"/>
+      <c r="S217" s="625"/>
       <c r="T217" s="518"/>
       <c r="U217" s="538"/>
       <c r="V217" s="538"/>
@@ -46330,7 +45304,7 @@
       </c>
       <c r="Q218" s="605"/>
       <c r="R218" s="606"/>
-      <c r="S218" s="653"/>
+      <c r="S218" s="625"/>
       <c r="T218" s="518"/>
       <c r="U218" s="538"/>
       <c r="V218" s="538"/>
@@ -46359,7 +45333,7 @@
       </c>
       <c r="Q219" s="605"/>
       <c r="R219" s="606"/>
-      <c r="S219" s="653"/>
+      <c r="S219" s="625"/>
       <c r="T219" s="518"/>
       <c r="U219" s="538"/>
       <c r="V219" s="538"/>
@@ -46388,7 +45362,7 @@
       </c>
       <c r="Q220" s="605"/>
       <c r="R220" s="606"/>
-      <c r="S220" s="653"/>
+      <c r="S220" s="625"/>
       <c r="T220" s="518"/>
       <c r="U220" s="538"/>
       <c r="V220" s="538"/>
@@ -46417,7 +45391,7 @@
       </c>
       <c r="Q221" s="605"/>
       <c r="R221" s="606"/>
-      <c r="S221" s="653"/>
+      <c r="S221" s="625"/>
       <c r="T221" s="518"/>
       <c r="U221" s="538"/>
       <c r="V221" s="538"/>
@@ -46446,7 +45420,7 @@
       </c>
       <c r="Q222" s="605"/>
       <c r="R222" s="606"/>
-      <c r="S222" s="653"/>
+      <c r="S222" s="625"/>
       <c r="T222" s="518"/>
       <c r="U222" s="538"/>
       <c r="V222" s="538"/>
@@ -46475,7 +45449,7 @@
       </c>
       <c r="Q223" s="605"/>
       <c r="R223" s="606"/>
-      <c r="S223" s="653"/>
+      <c r="S223" s="625"/>
       <c r="T223" s="518"/>
       <c r="U223" s="538"/>
       <c r="V223" s="538"/>
@@ -46504,7 +45478,7 @@
       </c>
       <c r="Q224" s="605"/>
       <c r="R224" s="606"/>
-      <c r="S224" s="653"/>
+      <c r="S224" s="625"/>
       <c r="T224" s="518"/>
       <c r="U224" s="439"/>
       <c r="V224" s="439"/>
@@ -46533,7 +45507,7 @@
       </c>
       <c r="Q225" s="605"/>
       <c r="R225" s="606"/>
-      <c r="S225" s="653"/>
+      <c r="S225" s="625"/>
       <c r="T225" s="518"/>
       <c r="U225" s="538"/>
       <c r="V225" s="538"/>
@@ -46562,7 +45536,7 @@
       </c>
       <c r="Q226" s="605"/>
       <c r="R226" s="606"/>
-      <c r="S226" s="653"/>
+      <c r="S226" s="625"/>
       <c r="T226" s="518"/>
       <c r="U226" s="538"/>
       <c r="V226" s="538"/>
@@ -46591,7 +45565,7 @@
       </c>
       <c r="Q227" s="605"/>
       <c r="R227" s="606"/>
-      <c r="S227" s="653"/>
+      <c r="S227" s="625"/>
       <c r="T227" s="518"/>
       <c r="U227" s="538"/>
       <c r="V227" s="538"/>
@@ -46620,7 +45594,7 @@
       </c>
       <c r="Q228" s="605"/>
       <c r="R228" s="606"/>
-      <c r="S228" s="653"/>
+      <c r="S228" s="625"/>
       <c r="T228" s="518"/>
       <c r="U228" s="538"/>
       <c r="V228" s="538"/>
@@ -46649,7 +45623,7 @@
       </c>
       <c r="Q229" s="605"/>
       <c r="R229" s="606"/>
-      <c r="S229" s="653"/>
+      <c r="S229" s="625"/>
       <c r="T229" s="518"/>
       <c r="U229" s="538"/>
       <c r="V229" s="538"/>
@@ -46678,7 +45652,7 @@
       </c>
       <c r="Q230" s="605"/>
       <c r="R230" s="606"/>
-      <c r="S230" s="653"/>
+      <c r="S230" s="625"/>
       <c r="T230" s="518"/>
       <c r="U230" s="538"/>
       <c r="V230" s="538"/>
@@ -46707,7 +45681,7 @@
       </c>
       <c r="Q231" s="605"/>
       <c r="R231" s="606"/>
-      <c r="S231" s="653"/>
+      <c r="S231" s="625"/>
       <c r="T231" s="518"/>
       <c r="U231" s="538"/>
       <c r="V231" s="538"/>
@@ -46736,7 +45710,7 @@
       </c>
       <c r="Q232" s="605"/>
       <c r="R232" s="606"/>
-      <c r="S232" s="653"/>
+      <c r="S232" s="625"/>
       <c r="T232" s="518"/>
       <c r="U232" s="439"/>
       <c r="V232" s="439"/>
@@ -46765,7 +45739,7 @@
       </c>
       <c r="Q233" s="605"/>
       <c r="R233" s="606"/>
-      <c r="S233" s="653"/>
+      <c r="S233" s="625"/>
       <c r="T233" s="518"/>
       <c r="U233" s="538"/>
       <c r="V233" s="538"/>
@@ -46794,7 +45768,7 @@
       </c>
       <c r="Q234" s="605"/>
       <c r="R234" s="606"/>
-      <c r="S234" s="653"/>
+      <c r="S234" s="625"/>
       <c r="T234" s="518"/>
       <c r="U234" s="538"/>
       <c r="V234" s="538"/>
@@ -46823,7 +45797,7 @@
       </c>
       <c r="Q235" s="605"/>
       <c r="R235" s="606"/>
-      <c r="S235" s="653"/>
+      <c r="S235" s="625"/>
       <c r="T235" s="518"/>
       <c r="U235" s="538"/>
       <c r="V235" s="538"/>
@@ -46852,7 +45826,7 @@
       </c>
       <c r="Q236" s="605"/>
       <c r="R236" s="606"/>
-      <c r="S236" s="653"/>
+      <c r="S236" s="625"/>
       <c r="T236" s="518"/>
       <c r="U236" s="538"/>
       <c r="V236" s="538"/>
@@ -46881,7 +45855,7 @@
       </c>
       <c r="Q237" s="605"/>
       <c r="R237" s="606"/>
-      <c r="S237" s="653"/>
+      <c r="S237" s="625"/>
       <c r="T237" s="518"/>
       <c r="U237" s="538"/>
       <c r="V237" s="538"/>
@@ -46910,7 +45884,7 @@
       </c>
       <c r="Q238" s="605"/>
       <c r="R238" s="606"/>
-      <c r="S238" s="653"/>
+      <c r="S238" s="625"/>
       <c r="T238" s="518"/>
       <c r="U238" s="538"/>
       <c r="V238" s="538"/>
@@ -46939,7 +45913,7 @@
       </c>
       <c r="Q239" s="605"/>
       <c r="R239" s="606"/>
-      <c r="S239" s="653"/>
+      <c r="S239" s="625"/>
       <c r="T239" s="518"/>
       <c r="U239" s="538"/>
       <c r="V239" s="538"/>
@@ -46968,7 +45942,7 @@
       </c>
       <c r="Q240" s="605"/>
       <c r="R240" s="606"/>
-      <c r="S240" s="653"/>
+      <c r="S240" s="625"/>
       <c r="T240" s="518"/>
       <c r="U240" s="538"/>
       <c r="V240" s="538"/>
@@ -46997,7 +45971,7 @@
       </c>
       <c r="Q241" s="605"/>
       <c r="R241" s="606"/>
-      <c r="S241" s="653"/>
+      <c r="S241" s="625"/>
       <c r="T241" s="518"/>
       <c r="U241" s="538"/>
       <c r="V241" s="538"/>
@@ -47026,7 +46000,7 @@
       </c>
       <c r="Q242" s="605"/>
       <c r="R242" s="606"/>
-      <c r="S242" s="653"/>
+      <c r="S242" s="625"/>
       <c r="T242" s="518"/>
       <c r="U242" s="538"/>
       <c r="V242" s="538"/>
@@ -47055,7 +46029,7 @@
       </c>
       <c r="Q243" s="605"/>
       <c r="R243" s="606"/>
-      <c r="S243" s="653"/>
+      <c r="S243" s="625"/>
       <c r="T243" s="518"/>
       <c r="U243" s="439"/>
       <c r="V243" s="439"/>
@@ -47084,7 +46058,7 @@
       </c>
       <c r="Q244" s="605"/>
       <c r="R244" s="606"/>
-      <c r="S244" s="653"/>
+      <c r="S244" s="625"/>
       <c r="T244" s="518"/>
       <c r="U244" s="538"/>
       <c r="V244" s="538"/>
@@ -47113,7 +46087,7 @@
       </c>
       <c r="Q245" s="605"/>
       <c r="R245" s="606"/>
-      <c r="S245" s="653"/>
+      <c r="S245" s="625"/>
       <c r="T245" s="518"/>
       <c r="U245" s="538"/>
       <c r="V245" s="538"/>
@@ -47142,7 +46116,7 @@
       </c>
       <c r="Q246" s="605"/>
       <c r="R246" s="606"/>
-      <c r="S246" s="653"/>
+      <c r="S246" s="625"/>
       <c r="T246" s="518"/>
       <c r="U246" s="538"/>
       <c r="V246" s="538"/>
@@ -47171,7 +46145,7 @@
       </c>
       <c r="Q247" s="605"/>
       <c r="R247" s="606"/>
-      <c r="S247" s="653"/>
+      <c r="S247" s="625"/>
       <c r="T247" s="518"/>
       <c r="U247" s="538"/>
       <c r="V247" s="538"/>
@@ -47200,7 +46174,7 @@
       </c>
       <c r="Q248" s="605"/>
       <c r="R248" s="606"/>
-      <c r="S248" s="653"/>
+      <c r="S248" s="625"/>
       <c r="T248" s="518"/>
       <c r="U248" s="538"/>
       <c r="V248" s="538"/>
@@ -47229,7 +46203,7 @@
       </c>
       <c r="Q249" s="605"/>
       <c r="R249" s="606"/>
-      <c r="S249" s="653"/>
+      <c r="S249" s="625"/>
       <c r="T249" s="518"/>
       <c r="U249" s="538"/>
       <c r="V249" s="538"/>
@@ -47258,7 +46232,7 @@
       </c>
       <c r="Q250" s="605"/>
       <c r="R250" s="606"/>
-      <c r="S250" s="653"/>
+      <c r="S250" s="625"/>
       <c r="T250" s="518"/>
       <c r="U250" s="538"/>
       <c r="V250" s="538"/>
@@ -47287,7 +46261,7 @@
       </c>
       <c r="Q251" s="605"/>
       <c r="R251" s="606"/>
-      <c r="S251" s="653"/>
+      <c r="S251" s="625"/>
       <c r="T251" s="518"/>
       <c r="U251" s="439"/>
       <c r="V251" s="439"/>
@@ -47316,7 +46290,7 @@
       </c>
       <c r="Q252" s="605"/>
       <c r="R252" s="606"/>
-      <c r="S252" s="653"/>
+      <c r="S252" s="625"/>
       <c r="T252" s="518"/>
       <c r="U252" s="538"/>
       <c r="V252" s="538"/>
@@ -47345,7 +46319,7 @@
       </c>
       <c r="Q253" s="605"/>
       <c r="R253" s="606"/>
-      <c r="S253" s="653"/>
+      <c r="S253" s="625"/>
       <c r="T253" s="518"/>
       <c r="U253" s="538"/>
       <c r="V253" s="538"/>
@@ -47374,7 +46348,7 @@
       </c>
       <c r="Q254" s="605"/>
       <c r="R254" s="606"/>
-      <c r="S254" s="653"/>
+      <c r="S254" s="625"/>
       <c r="T254" s="518"/>
       <c r="U254" s="538"/>
       <c r="V254" s="538"/>
@@ -47403,7 +46377,7 @@
       </c>
       <c r="Q255" s="605"/>
       <c r="R255" s="606"/>
-      <c r="S255" s="653"/>
+      <c r="S255" s="625"/>
       <c r="T255" s="518"/>
       <c r="U255" s="538"/>
       <c r="V255" s="538"/>
@@ -47432,7 +46406,7 @@
       </c>
       <c r="Q256" s="605"/>
       <c r="R256" s="606"/>
-      <c r="S256" s="653"/>
+      <c r="S256" s="625"/>
       <c r="T256" s="518"/>
       <c r="U256" s="538"/>
       <c r="V256" s="538"/>
@@ -47461,7 +46435,7 @@
       </c>
       <c r="Q257" s="605"/>
       <c r="R257" s="606"/>
-      <c r="S257" s="653"/>
+      <c r="S257" s="625"/>
       <c r="T257" s="518"/>
       <c r="U257" s="538"/>
       <c r="V257" s="538"/>
@@ -47490,7 +46464,7 @@
       </c>
       <c r="Q258" s="605"/>
       <c r="R258" s="606"/>
-      <c r="S258" s="653"/>
+      <c r="S258" s="625"/>
       <c r="T258" s="518"/>
       <c r="U258" s="538"/>
       <c r="V258" s="538"/>
@@ -47519,7 +46493,7 @@
       </c>
       <c r="Q259" s="605"/>
       <c r="R259" s="606"/>
-      <c r="S259" s="653"/>
+      <c r="S259" s="625"/>
       <c r="T259" s="518"/>
       <c r="U259" s="439"/>
       <c r="V259" s="439"/>
@@ -47710,7 +46684,6 @@
     <brk id="11" max="1048575" man="1"/>
     <brk id="13" max="1048575" man="1"/>
   </colBreaks>
-  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -47864,55 +46837,55 @@
       <c r="B2" s="414" t="s">
         <v>42</v>
       </c>
-      <c r="G2" s="644"/>
-      <c r="H2" s="644"/>
-      <c r="I2" s="644"/>
+      <c r="G2" s="651"/>
+      <c r="H2" s="651"/>
+      <c r="I2" s="651"/>
     </row>
     <row r="4" spans="2:12">
-      <c r="B4" s="643" t="s">
+      <c r="B4" s="650" t="s">
         <v>43</v>
       </c>
-      <c r="C4" s="643" t="s">
+      <c r="C4" s="650" t="s">
         <v>44</v>
       </c>
-      <c r="D4" s="645" t="s">
+      <c r="D4" s="652" t="s">
         <v>45</v>
       </c>
-      <c r="E4" s="645" t="s">
+      <c r="E4" s="652" t="s">
         <v>122</v>
       </c>
-      <c r="F4" s="645" t="s">
+      <c r="F4" s="652" t="s">
         <v>46</v>
       </c>
-      <c r="G4" s="643" t="s">
+      <c r="G4" s="650" t="s">
         <v>47</v>
       </c>
-      <c r="H4" s="643"/>
-      <c r="I4" s="643" t="s">
+      <c r="H4" s="650"/>
+      <c r="I4" s="650" t="s">
         <v>48</v>
       </c>
-      <c r="J4" s="643" t="s">
+      <c r="J4" s="650" t="s">
         <v>49</v>
       </c>
-      <c r="K4" s="643" t="s">
+      <c r="K4" s="650" t="s">
         <v>118</v>
       </c>
-      <c r="L4" s="643"/>
+      <c r="L4" s="650"/>
     </row>
     <row r="5" spans="2:12">
-      <c r="B5" s="643"/>
-      <c r="C5" s="643"/>
-      <c r="D5" s="646"/>
-      <c r="E5" s="646"/>
-      <c r="F5" s="646"/>
+      <c r="B5" s="650"/>
+      <c r="C5" s="650"/>
+      <c r="D5" s="653"/>
+      <c r="E5" s="653"/>
+      <c r="F5" s="653"/>
       <c r="G5" s="418" t="s">
         <v>50</v>
       </c>
       <c r="H5" s="417" t="s">
         <v>61</v>
       </c>
-      <c r="I5" s="643"/>
-      <c r="J5" s="643"/>
+      <c r="I5" s="650"/>
+      <c r="J5" s="650"/>
       <c r="K5" s="417" t="s">
         <v>119</v>
       </c>

--- a/작업장소 (영수증 보관)/심천지사 전도금 정산 양식_YYYY-MM.xlsx
+++ b/작업장소 (영수증 보관)/심천지사 전도금 정산 양식_YYYY-MM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\20000177\Desktop\Wooktigravity\260630_shenzhen_restart_step_1\작업장소 (영수증 보관)\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{07F9C168-9BC2-4D41-B611-184E8313F698}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{953095EC-B75E-4E96-B7C7-16A8D321678E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="735" yWindow="735" windowWidth="21600" windowHeight="11295" tabRatio="603" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="통장내역(환율표)" sheetId="131" r:id="rId1"/>
@@ -38830,17 +38830,17 @@
     </sortState>
   </autoFilter>
   <mergeCells count="11">
-    <mergeCell ref="H17:J17"/>
-    <mergeCell ref="K17:M17"/>
-    <mergeCell ref="N17:O17"/>
-    <mergeCell ref="P17:Q17"/>
-    <mergeCell ref="P18:Q18"/>
     <mergeCell ref="R103:R107"/>
     <mergeCell ref="R79:R83"/>
     <mergeCell ref="R84:R88"/>
     <mergeCell ref="R89:R93"/>
     <mergeCell ref="R94:R98"/>
     <mergeCell ref="R99:R102"/>
+    <mergeCell ref="H17:J17"/>
+    <mergeCell ref="K17:M17"/>
+    <mergeCell ref="N17:O17"/>
+    <mergeCell ref="P17:Q17"/>
+    <mergeCell ref="P18:Q18"/>
   </mergeCells>
   <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
